--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B59FEF0-FBE9-48DE-B5FB-BD96A57CAE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F01FE71-F81C-4379-82AD-4B7B4662E138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -157,18 +157,6 @@
     <t>ARPEGIO - Omega - Mauricio Murúa</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1emXUmJs70wS68hiq71bHrOGz0TUur4Gh&amp;usp=drive_fs</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=13Tnhbuvbr9lMHz0-UYtuZpa5KuMeiXA-&amp;usp=drive_fs</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1aEnjg_0osW5eYm01nzSiAuPwdZFB3xuS&amp;usp=drive_fs</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1xezm-2cxHGI2nSFzCnX4QP3uI-bE5rXT&amp;usp=drive_fs</t>
-  </si>
-  <si>
     <t>Ćwiczenie na ogrywanie akordów za pomocą systemu CAGED. Dzięki niemu ograsz wszystkie przewroty akordów wzdłóż gryfu.</t>
   </si>
   <si>
@@ -179,6 +167,18 @@
   </si>
   <si>
     <t>Krótka etiuda ogrywająca akordy w ciekawy sposób.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/uc?export=view&amp;id=1emXUmJs70wS68hiq71bHrOGz0TUur4Gh</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/uc?export=view&amp;id=13Tnhbuvbr9lMHz0-UYtuZpa5KuMeiXA-</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/uc?export=view&amp;id=1aEnjg_0osW5eYm01nzSiAuPwdZFB3xuS</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/uc?export=view&amp;id=1xezm-2cxHGI2nSFzCnX4QP3uI-bE5rXT</t>
   </si>
 </sst>
 </file>
@@ -646,10 +646,10 @@
         <v>36</v>
       </c>
       <c r="F2" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -669,10 +669,10 @@
         <v>37</v>
       </c>
       <c r="F3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -692,10 +692,10 @@
         <v>38</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -715,10 +715,10 @@
         <v>39</v>
       </c>
       <c r="F5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -748,10 +748,10 @@
     <hyperlink ref="E3" r:id="rId2" xr:uid="{B41FAB88-E51F-43D8-B057-ACD206F129FB}"/>
     <hyperlink ref="E4" r:id="rId3" xr:uid="{14B9C1B5-749C-4628-A58D-91E70CDE055B}"/>
     <hyperlink ref="E5" r:id="rId4" xr:uid="{7B793A24-6321-4979-B5CA-05E4D6AC508F}"/>
-    <hyperlink ref="F2" r:id="rId5" xr:uid="{23132CF4-8A0D-40A4-843B-5F60F4DF4864}"/>
-    <hyperlink ref="F3" r:id="rId6" xr:uid="{D8320BEE-2538-429C-A448-28FADAFFB720}"/>
-    <hyperlink ref="F4" r:id="rId7" xr:uid="{9E805AD2-400A-4DEE-A2EC-7F39F4D305A1}"/>
-    <hyperlink ref="F5" r:id="rId8" xr:uid="{D0F8C780-CFAE-4C3F-B39E-8233AAA41BA7}"/>
+    <hyperlink ref="F2" r:id="rId5" xr:uid="{C1B1F1B0-FD9E-4F9F-9667-A8D0FE1D2301}"/>
+    <hyperlink ref="F3" r:id="rId6" xr:uid="{80148996-AA01-4363-8791-6C80DAB9C19E}"/>
+    <hyperlink ref="F4" r:id="rId7" xr:uid="{372160D2-5864-4F82-8F09-843530621722}"/>
+    <hyperlink ref="F5" r:id="rId8" xr:uid="{B0915ADB-C36F-4888-9665-B761F556F9B8}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C64C19-944F-4F13-9732-C387CC4041CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D59735-5BD3-4A97-B4EC-6A251AFF9480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -276,7 +276,7 @@
     <t xml:space="preserve">Ćwiczenie na niezależne granie melodii oraz basu jednocześnie w rytmie lekkiego shuffle. </t>
   </si>
   <si>
-    <t xml:space="preserve">ECONOMY PICKING - Two Strings, Two Directions </t>
+    <t>ECONOMY PICKING - Two Strings, Two Directions</t>
   </si>
 </sst>
 </file>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5F07E4-E1E5-4253-91C2-B7FF9AF65157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1556886-E440-46F8-BD8C-C82F729D17AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1556886-E440-46F8-BD8C-C82F729D17AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8ECD93-9B74-4B58-B10F-1141C022CE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="80">
   <si>
     <t>NAZWA</t>
   </si>
@@ -60,12 +60,6 @@
     <t>OPIS</t>
   </si>
   <si>
-    <t>Średni</t>
-  </si>
-  <si>
-    <t>Zaawansowany</t>
-  </si>
-  <si>
     <t>W SZPONACH GITARY — INSTRUKCJA ARKUSZA</t>
   </si>
   <si>
@@ -222,9 +216,6 @@
     <t xml:space="preserve">Ćwiczenie na ogrywanie akordów pazurkiem w stylu Thomiego Emanuela i Cheta Atkinsa. </t>
   </si>
   <si>
-    <t>Prosty</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ćwiczenie na slapy perkusyjne oraz ogrywanie akordów. </t>
   </si>
   <si>
@@ -277,6 +268,15 @@
   </si>
   <si>
     <t>ECONOMY PICKING - Two Strings Two Directions</t>
+  </si>
+  <si>
+    <t>ŚREDNI</t>
+  </si>
+  <si>
+    <t>PROSTY</t>
+  </si>
+  <si>
+    <t>ZAAWANSOWANY</t>
   </si>
 </sst>
 </file>
@@ -730,273 +730,275 @@
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1122,7 +1124,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1130,42 +1132,42 @@
     </row>
     <row r="3" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1173,37 +1175,37 @@
     </row>
     <row r="12" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8ECD93-9B74-4B58-B10F-1141C022CE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89699834-4A97-415C-A4E0-41DBA4621203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -276,7 +276,7 @@
     <t>PROSTY</t>
   </si>
   <si>
-    <t>ZAAWANSOWANY</t>
+    <t>TRUDNY</t>
   </si>
 </sst>
 </file>
@@ -1111,6 +1111,7 @@
     <hyperlink ref="E13" r:id="rId7" xr:uid="{4281A67C-AC78-4A68-A664-CAB0381ADAA6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
 

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A952A7E-0818-4F00-BF0B-263537D69CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77887DA-9271-4081-95FA-BC7FEE9068A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ćwiczenia" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="182">
   <si>
     <t>NAZWA</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>LINK</t>
-  </si>
-  <si>
-    <t>LINK DO OKŁADKI</t>
   </si>
   <si>
     <t>OPIS</t>
@@ -593,7 +590,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -624,6 +621,22 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC8A84B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="5">
@@ -677,7 +690,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -699,6 +712,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1003,20 +1025,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="6" width="2.42578125" customWidth="1"/>
-    <col min="7" max="7" width="60" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1029,1028 +1050,1211 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="D8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="D29" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D32" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D33" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D34" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="D35" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="D37" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D38" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F25" s="7"/>
-      <c r="G25" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="E39" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="F29" s="7"/>
-      <c r="G29" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="E40" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="E41" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E42" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="7"/>
-      <c r="G31" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="F33" s="7"/>
-      <c r="G33" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="F35" s="7"/>
-      <c r="G35" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="F37" s="7"/>
-      <c r="G37" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="F38" s="7"/>
-      <c r="G38" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="F39" s="7"/>
-      <c r="G39" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F40" s="7"/>
-      <c r="G40" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F41" s="7"/>
-      <c r="G41" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="F42" s="6"/>
-      <c r="G42" s="2" t="s">
+      <c r="C43" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="F43" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E43" s="7" t="s">
+    </row>
+    <row r="44" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F43" s="7"/>
-      <c r="G43" s="3" t="s">
+      <c r="B44" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+      <c r="F44" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="F44" s="6"/>
-      <c r="G44" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="3"/>
-    </row>
-    <row r="46" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E45" s="3"/>
+      <c r="F45" s="9"/>
+    </row>
+    <row r="46" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E46" s="2"/>
+      <c r="F46" s="8"/>
+    </row>
+    <row r="47" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="3"/>
-    </row>
-    <row r="48" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E47" s="3"/>
+      <c r="F47" s="9"/>
+    </row>
+    <row r="48" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E48" s="2"/>
+      <c r="F48" s="8"/>
+    </row>
+    <row r="49" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="3"/>
-    </row>
-    <row r="50" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E49" s="3"/>
+      <c r="F49" s="9"/>
+    </row>
+    <row r="50" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="2"/>
-    </row>
-    <row r="51" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E50" s="2"/>
+      <c r="F50" s="8"/>
+    </row>
+    <row r="51" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="3"/>
-    </row>
-    <row r="52" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E51" s="3"/>
+      <c r="F51" s="9"/>
+    </row>
+    <row r="52" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="2"/>
-    </row>
-    <row r="53" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E52" s="2"/>
+      <c r="F52" s="8"/>
+    </row>
+    <row r="53" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="3"/>
-    </row>
-    <row r="54" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E53" s="3"/>
+      <c r="F53" s="9"/>
+    </row>
+    <row r="54" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="2"/>
-    </row>
-    <row r="55" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E54" s="2"/>
+      <c r="F54" s="8"/>
+    </row>
+    <row r="55" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="9"/>
+    </row>
+    <row r="56" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="9"/>
+    </row>
+    <row r="57" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="8"/>
+    </row>
+    <row r="58" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="9"/>
+    </row>
+    <row r="59" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="8"/>
+    </row>
+    <row r="60" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="9"/>
+    </row>
+    <row r="61" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="8"/>
+    </row>
+    <row r="62" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="9"/>
+    </row>
+    <row r="63" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="8"/>
+    </row>
+    <row r="64" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="9"/>
+    </row>
+    <row r="65" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="8"/>
+    </row>
+    <row r="66" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="9"/>
+    </row>
+    <row r="67" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="8"/>
+    </row>
+    <row r="68" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="9"/>
+    </row>
+    <row r="69" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="8"/>
+    </row>
+    <row r="70" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="9"/>
+    </row>
+    <row r="71" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="8"/>
+    </row>
+    <row r="72" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="9"/>
+    </row>
+    <row r="73" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="8"/>
+    </row>
+    <row r="74" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="9"/>
+    </row>
+    <row r="75" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="8"/>
+    </row>
+    <row r="76" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="9"/>
+    </row>
+    <row r="77" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="8"/>
+    </row>
+    <row r="78" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="9"/>
+    </row>
+    <row r="79" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="8"/>
+    </row>
+    <row r="80" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="9"/>
+    </row>
+    <row r="81" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="8"/>
+    </row>
+    <row r="82" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="9"/>
+    </row>
+    <row r="83" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="8"/>
+    </row>
+    <row r="84" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="9"/>
+    </row>
+    <row r="85" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{D1A2F6F8-0B0C-45AC-8503-47F91AE15E78}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{B41FAB88-E51F-43D8-B057-ACD206F129FB}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{14B9C1B5-749C-4628-A58D-91E70CDE055B}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{7B793A24-6321-4979-B5CA-05E4D6AC508F}"/>
-    <hyperlink ref="E6" r:id="rId5" xr:uid="{49C2C9A7-BE41-4991-BAF1-1114754E4D52}"/>
-    <hyperlink ref="E7" r:id="rId6" xr:uid="{5570D874-FCDF-4C3C-9661-A9607E3ADEEB}"/>
-    <hyperlink ref="E13" r:id="rId7" xr:uid="{4281A67C-AC78-4A68-A664-CAB0381ADAA6}"/>
-    <hyperlink ref="E17" r:id="rId8" xr:uid="{C020F178-7F0C-4255-84C0-D02096F78587}"/>
-    <hyperlink ref="E19" r:id="rId9" xr:uid="{32919252-880A-47F2-A773-C93662E9BCDB}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{D1A2F6F8-0B0C-45AC-8503-47F91AE15E78}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{B41FAB88-E51F-43D8-B057-ACD206F129FB}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{14B9C1B5-749C-4628-A58D-91E70CDE055B}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{7B793A24-6321-4979-B5CA-05E4D6AC508F}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{49C2C9A7-BE41-4991-BAF1-1114754E4D52}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{5570D874-FCDF-4C3C-9661-A9607E3ADEEB}"/>
+    <hyperlink ref="F13" r:id="rId7" xr:uid="{4281A67C-AC78-4A68-A664-CAB0381ADAA6}"/>
+    <hyperlink ref="F17" r:id="rId8" xr:uid="{C020F178-7F0C-4255-84C0-D02096F78587}"/>
+    <hyperlink ref="F19" r:id="rId9" xr:uid="{32919252-880A-47F2-A773-C93662E9BCDB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
@@ -2067,7 +2271,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2075,42 +2279,42 @@
     </row>
     <row r="3" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2118,37 +2322,37 @@
     </row>
     <row r="12" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A884CCC-DF99-44E8-B5B1-9687000F55B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA9A527-4746-440D-B76B-21D71F7908A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ćwiczenia" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="257">
   <si>
     <t>NAZWA</t>
   </si>
@@ -592,12 +592,6 @@
     <t>https://drive.google.com/open?id=1ZYPlbvt7LT_Z7hwdvGMu8oWL9jqXsC_f&amp;usp=drive_fs</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1s-jnwyHdJS9RMrxxxyG6-nly3-XcPv1F&amp;usp=drive_fs</t>
-  </si>
-  <si>
-    <t>SPIDER - Pajączek 3D B</t>
-  </si>
-  <si>
     <t>SPIDER - Pajączek 3D A</t>
   </si>
   <si>
@@ -619,9 +613,6 @@
     <t>SPIDER - String Switching Spider</t>
   </si>
   <si>
-    <t>SPIDER -Spider Finger Combinations</t>
-  </si>
-  <si>
     <t>https://drive.google.com/open?id=1P119t3n2xVcYfuZBsyTX3_CumK2M4SmE&amp;usp=drive_fs</t>
   </si>
   <si>
@@ -643,9 +634,6 @@
     <t>https://drive.google.com/open?id=1a9ZZdJlreI20ElUs70EAL7VIQ161PTx5&amp;usp=drive_fs</t>
   </si>
   <si>
-    <t>STRENGTH AND STRETCH</t>
-  </si>
-  <si>
     <t>STRENGTH AND STRETCH - Burning Hands</t>
   </si>
   <si>
@@ -779,6 +767,48 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1OLTVJWy69Xttg0oIB-2MaDhPww_eAu3A&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider, </t>
+  </si>
+  <si>
+    <t>ROZCIĄGANIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rozciąganie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">String Skipping, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweep Picking, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synchronizacja, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utwory, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rozgrzewka, Synchronizacja, Szybkość, Płynność, Wprawki, Picking, Lewa Ręka, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider, Picking, Synchronizacja, Wprawki, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider, String Skipping, Synchronizacja, Lewa Ręka, Wprawki, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider, Lewa Ręka, Synchronizacja, Niezależność palców, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider, Zmiana Strun, Lewa Ręka, Picking, Pick Slanting, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider, Speed Burst, Niezależność palców, </t>
+  </si>
+  <si>
+    <t>SPIDER - Spider Finger Combinations</t>
   </si>
 </sst>
 </file>
@@ -1220,7 +1250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -2113,505 +2143,561 @@
     </row>
     <row r="45" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
+      <c r="C45" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="E45" s="3"/>
       <c r="F45" s="9" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="3" t="s">
         <v>185</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="8" t="s">
-        <v>184</v>
+      <c r="C46" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="9" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>187</v>
+      <c r="A47" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="9" t="s">
-        <v>194</v>
+      <c r="C47" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" s="8" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>188</v>
+      <c r="A48" s="3" t="s">
+        <v>187</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="8" t="s">
-        <v>195</v>
+      <c r="C48" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="9" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>189</v>
+      <c r="A49" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="9" t="s">
-        <v>196</v>
+      <c r="C49" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" s="8" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>190</v>
+      <c r="A50" s="3" t="s">
+        <v>189</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="8" t="s">
-        <v>197</v>
+      <c r="C50" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="9" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>191</v>
+      <c r="A51" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="9" t="s">
-        <v>198</v>
+      <c r="C51" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" s="8" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>192</v>
+      <c r="A52" s="3" t="s">
+        <v>256</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="8" t="s">
+      <c r="C52" s="3"/>
+      <c r="D52" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" s="8" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="9" t="s">
+    <row r="54" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
+      <c r="C54" s="3"/>
+      <c r="D54" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="8" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
+      <c r="D55" s="3" t="s">
+        <v>246</v>
+      </c>
       <c r="E55" s="3"/>
       <c r="F55" s="9" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" s="8" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
+    <row r="57" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="9" t="s">
+      <c r="B57" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="9" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
+    <row r="58" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="8" t="s">
+      <c r="B58" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" s="8" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
+    <row r="59" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="9" t="s">
+      <c r="B59" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E59" s="3"/>
+      <c r="F59" s="9" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
+    <row r="60" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="8" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
+      <c r="C60" s="2"/>
+      <c r="D60" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="9" t="s">
+    </row>
+    <row r="61" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
+      <c r="B61" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" s="9" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="8" t="s">
+      <c r="B62" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" s="8" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
+    <row r="63" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="9" t="s">
+      <c r="B63" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E63" s="3"/>
+      <c r="F63" s="9" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
+    <row r="64" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="8" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
+      <c r="C64" s="2"/>
+      <c r="D64" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="9" t="s">
+    </row>
+    <row r="65" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
+      <c r="C65" s="3"/>
+      <c r="D65" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E65" s="3"/>
+      <c r="F65" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="8" t="s">
+    </row>
+    <row r="66" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
+      <c r="B66" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="9" t="s">
+      <c r="B67" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="F67" s="9" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
+    <row r="68" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="6" t="s">
+      <c r="B68" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" s="8" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
+    <row r="69" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="9" t="s">
+      <c r="B69" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E69" s="3"/>
+      <c r="F69" s="9" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
+    <row r="70" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="8" t="s">
+      <c r="B70" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" s="8" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
+    <row r="71" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="9" t="s">
+      <c r="B71" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E71" s="3"/>
+      <c r="F71" s="9" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
+    <row r="72" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="8" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
+      <c r="C72" s="2"/>
+      <c r="D72" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="9" t="s">
-        <v>243</v>
-      </c>
     </row>
     <row r="73" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="8" t="s">
-        <v>246</v>
-      </c>
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="9"/>
     </row>
     <row r="74" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="9"/>
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="8"/>
     </row>
     <row r="75" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="8"/>
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="9"/>
     </row>
     <row r="76" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="9"/>
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="8"/>
     </row>
     <row r="77" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="8"/>
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="9"/>
     </row>
     <row r="78" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="9"/>
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="8"/>
     </row>
     <row r="79" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="8"/>
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="9"/>
     </row>
     <row r="80" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="9"/>
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="8"/>
     </row>
     <row r="81" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="8"/>
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="9"/>
     </row>
     <row r="82" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-      <c r="F82" s="9"/>
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="8"/>
     </row>
     <row r="83" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="8"/>
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="9"/>
     </row>
     <row r="84" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="9"/>
-    </row>
-    <row r="85" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="8"/>
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2624,7 +2710,7 @@
     <hyperlink ref="F13" r:id="rId7" xr:uid="{4281A67C-AC78-4A68-A664-CAB0381ADAA6}"/>
     <hyperlink ref="F17" r:id="rId8" xr:uid="{C020F178-7F0C-4255-84C0-D02096F78587}"/>
     <hyperlink ref="F19" r:id="rId9" xr:uid="{32919252-880A-47F2-A773-C93662E9BCDB}"/>
-    <hyperlink ref="F67" r:id="rId10" xr:uid="{D2B6880C-A11D-476C-9E19-250564686AE4}"/>
+    <hyperlink ref="F66" r:id="rId10" xr:uid="{D2B6880C-A11D-476C-9E19-250564686AE4}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA9A527-4746-440D-B76B-21D71F7908A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9352E266-1ACD-454C-BDC7-52019DC406BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="259">
   <si>
     <t>NAZWA</t>
   </si>
@@ -592,9 +592,6 @@
     <t>https://drive.google.com/open?id=1ZYPlbvt7LT_Z7hwdvGMu8oWL9jqXsC_f&amp;usp=drive_fs</t>
   </si>
   <si>
-    <t>SPIDER - Pajączek 3D A</t>
-  </si>
-  <si>
     <t>SPIDER - Pajączek Pionowy</t>
   </si>
   <si>
@@ -809,6 +806,15 @@
   </si>
   <si>
     <t>SPIDER - Spider Finger Combinations</t>
+  </si>
+  <si>
+    <t>ŚREDNI, TRUDNY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider, Zmiana Strun, Lewa Ręka, Niezależność palców, Pick Slanting, </t>
+  </si>
+  <si>
+    <t>SPIDER - Pajączek 3D</t>
   </si>
 </sst>
 </file>
@@ -2143,7 +2149,7 @@
     </row>
     <row r="45" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>184</v>
+        <v>258</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>182</v>
@@ -2152,7 +2158,7 @@
         <v>78</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="9" t="s">
@@ -2161,7 +2167,7 @@
     </row>
     <row r="46" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>182</v>
@@ -2170,16 +2176,16 @@
         <v>76</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>182</v>
@@ -2188,16 +2194,16 @@
         <v>77</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>182</v>
@@ -2206,16 +2212,16 @@
         <v>78</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>182</v>
@@ -2224,16 +2230,16 @@
         <v>78</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>182</v>
@@ -2242,16 +2248,16 @@
         <v>76</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>182</v>
@@ -2260,347 +2266,363 @@
         <v>77</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C52" s="3"/>
+      <c r="C52" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="D52" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C54" s="3"/>
+        <v>199</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="D54" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C55" s="3"/>
+        <v>199</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="D55" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="D56" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C57" s="3"/>
+        <v>199</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="D57" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="D58" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C59" s="3"/>
+        <v>199</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="D59" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C71" s="3"/>
       <c r="D71" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9352E266-1ACD-454C-BDC7-52019DC406BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080F5A10-E3E3-45D0-8603-A9BB591576E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="310">
   <si>
     <t>NAZWA</t>
   </si>
@@ -228,9 +228,6 @@
     <t>Pick Slanting, Shred, Picking, Synchronizacja, Lewa Ręka</t>
   </si>
   <si>
-    <t xml:space="preserve">Szybkość, Płynność, Lewa Ręka, </t>
-  </si>
-  <si>
     <t>Synchronizacja, Precyzja, Rytm</t>
   </si>
   <si>
@@ -402,9 +399,6 @@
     <t>PICKING</t>
   </si>
   <si>
-    <t xml:space="preserve">Picking, </t>
-  </si>
-  <si>
     <t>RYTM</t>
   </si>
   <si>
@@ -511,12 +505,6 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1uDF3pG6LuDEM8eWx3CSKJ-lPbyaX4wAj&amp;usp=drive_fs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rytm, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shred, </t>
   </si>
   <si>
     <t>PROSTY, ŚREDNI, TRUDNY</t>
@@ -766,42 +754,18 @@
     <t>https://drive.google.com/open?id=1OLTVJWy69Xttg0oIB-2MaDhPww_eAu3A&amp;usp=drive_fs</t>
   </si>
   <si>
-    <t xml:space="preserve">Spider, </t>
-  </si>
-  <si>
     <t>ROZCIĄGANIE</t>
   </si>
   <si>
-    <t xml:space="preserve">Rozciąganie, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">String Skipping, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweep Picking, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Synchronizacja, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utwory, </t>
-  </si>
-  <si>
     <t xml:space="preserve">Rozgrzewka, Synchronizacja, Szybkość, Płynność, Wprawki, Picking, Lewa Ręka, </t>
   </si>
   <si>
     <t xml:space="preserve">Spider, Picking, Synchronizacja, Wprawki, </t>
   </si>
   <si>
-    <t xml:space="preserve">Spider, String Skipping, Synchronizacja, Lewa Ręka, Wprawki, </t>
-  </si>
-  <si>
     <t xml:space="preserve">Spider, Lewa Ręka, Synchronizacja, Niezależność palców, </t>
   </si>
   <si>
-    <t xml:space="preserve">Spider, Zmiana Strun, Lewa Ręka, Picking, Pick Slanting, </t>
-  </si>
-  <si>
     <t xml:space="preserve">Spider, Speed Burst, Niezależność palców, </t>
   </si>
   <si>
@@ -815,6 +779,195 @@
   </si>
   <si>
     <t>SPIDER - Pajączek 3D</t>
+  </si>
+  <si>
+    <t>Ćwiczenie, dzięki któremu solidnie poćwiczysz zmianę strun, wraz z wykonywaniem pajączka.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To najbardziej klasyczna wersja "pajączka". Grasz cztery progi czterema palcami, a następnie schodzisz na kolejną strunę. </t>
+  </si>
+  <si>
+    <t>Tym razem zagrasz pajączka, próg po progu, palec po palcu, ale wzdłuż struny, przesuwając się za każdym razem o jeden próg dalej.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To ćwiczenie to czysta matematyka i zawiera każdą możliwą kombinację opalcowania, jaką możesz stworzyć. Świetne, jeżeli chcesz nauczyć swoje palce poruszać się całkowicie niezależnie. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzięki temu ćwiczeniu skupisz się bardziej na prawej ręce, ucząc się zmieniać strunę za pomocą pochylenia płaszczyzny kostkowania, tzw. "Pick Slantingu". </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zbuduj szybkość grania, bazując na Speed Burstach. Edycja pajączki. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzięki temu zwariowanemu ćwiczeniu zbudujesz zarówno prędkość, niezależność poruszania się palców lewej dłoni, jak i połączysz to wszystko z synchronizowaniem obu dłoni. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">To ćwiczenie to dosłownie siłownia dla twoich palców. Poćwicz je przez miesiąc. A efekty przerosną twoje oczekiwania. </t>
+  </si>
+  <si>
+    <t>Szalone ćwiczenie pajączków, które brzmi dosłownie jak shred. Popracujesz nad koordynacją palców lewej dłoni i zmianą strun przy użyciu pick slantingu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzięki temu ćwiczeniu lepiej opanujesz zmianę strun za pomocą pochylania płaszczyzny kostkowania. </t>
+  </si>
+  <si>
+    <t>String Skipping, Pick Slanting, Synchronizacja, Shred, Alternate Picking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzięki tej etiudzie opanujesz przeskakiwanie między strunami, bez nudzenia się podczas standardowych ćwiczeń. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">String Skipping, Alternate Picking, Etiuda, Shred, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">To ćwiczenie od Johna Petrucciego nauczy cię przeskakiwać struny za pomocą kształtów akordów oraz różnej ilości dźwięków na strunę. Szczególnie trudno jest zagrać trzy dźwięki na strune. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">String Skipping, Alternate Picking, Wprawki, </t>
+  </si>
+  <si>
+    <t>To ćwiczenie na string skipping wykorzystuje pierwszy bok z pentatoniki molowej i przeskakuje przez trzy struny.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">String Skipping, Skale, Alternate Picking, Lewa Ręka, Szybkość, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">To ćwiczenie powstało w oparciu o sekwencję pentatoniki oraz zmianę strun w przewidywalny sposób. Jego największą mocą jest nauczenie się wszystkich boxów w najlepszych możliwych opalcowaniach. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">String Skipping, Skale, Etiuda, Alternate Picking, Lewa Ręka, </t>
+  </si>
+  <si>
+    <t>Ćwiczenie na przeskakiwanie strun jest oparte na skali muzycznej oraz popularnych opalcowaniach.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">String Skipping, Skale, Alternate Picking, Wprawki, Płynność, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etiuda, dzięki której połączysz sweep picking razem z normalnie granymi dźwiękami. Przy okazji brzmi gniajnie jako podkład do improwizacji. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweep Picking, Arpeggio, Etiuda, Synchronizacja, Alternate Picking, </t>
+  </si>
+  <si>
+    <t>To ćwiczenie jest świetne zarówno na trening sweep pickingu, jak i poznanie wszystkich rodzajów arpeggio granych przez 5 strun.</t>
+  </si>
+  <si>
+    <t>To ćwiczenie jest świetne zarówno na trening sweep pickingu, jak i poznanie wszystkich rodzajów arpeggio granych przez 6 strun.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na synchronizację lewej i prawej dłoni zbudowane w oparciu o jedną strunę oraz ciekawy układ, przypominający trochę "Thunderstrucka", lecz z innym wariantem rytmicznym. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweep Picking, Etiuda, Arpeggio, </t>
+  </si>
+  <si>
+    <t>Synchronizacja, Lewa Ręka, Prawa Ręka, Alternate Picking, Rytm</t>
+  </si>
+  <si>
+    <t>Świetnie brzmiąca etiuda, w której podczas sweepowania opanujesz wiele rodzajów arpeggio, w stylu Yngwie Malmsten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweep Picking, Arpeggio, Akordy, Synchronizacja, </t>
+  </si>
+  <si>
+    <t>Ten utwór doskonale synchronizuje obie dłonie i uczy, jak używać minimalnego nacisku. Kluczowe jest granie z rozluźnioną dłonią.</t>
+  </si>
+  <si>
+    <t>To bardzo wymagający utwór, skupiający wokół siebie bardzo wiele technicznych zagadnień. Jeśli umiesz zagrać ten utwór w pełnym tempie, to jesteś kozak.</t>
+  </si>
+  <si>
+    <t>Ten utwór to bardzo ciekawa etiuda na sweep, picking oraz shredowanie. Myślę, że nie będzie to niespodzianką, że tę wersję zaaranżował Yngwie Malmsteen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten z pozoru niewinny utwór to prawdziwa kuźnia shreddowego grania. Dzięki niemu opanujesz zmianę strun w naprawdę szybkim tempie. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">To bardzo fajny utwór, dzięki któremu solidnie poćwiczysz. Ma ciekawy układ opalcowania oraz speed bursty w triolowym rytmie. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzięki temu utworowi opanujesz zmianę strun oraz synchronizację obu dłoni. Kto powiedział, że klasyka nie nadaje się do gitarowych ćwiczeń? </t>
+  </si>
+  <si>
+    <t>Jeden z bardziej wymagających utworów, zawierający całą masę trudnych technicznych momentów.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jest to bardzo proste w swojej konstrukcji ćwiczenie, jednak nie uwierzysz, jaki wycisk potrafi dać twoim palcom. Największa rada to granie tylko jednym palcem na raz, za pomocą minimalnej siły docisku, dzięki której zachowasz rozluźnienie dłoni niezbędne do płynnej gry. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Picking, Speed Burst, Alternate Picking, Rytm, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rytm, Wprawki, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rytm, Picking, Alternate Picking, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shred, Alternate Picking, Speed Burst, Wprawki, Etiuda, Synchronizacja, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shred, Alternate Picking, Synchronizacja, Szybkość, Skale, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shred, Skale, Alternate Picking, Pick Slanting, Płynność, Szybkość, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shred, Alternate Picking, Synchronizacja, Pick Slanting, Płynność, Niezależność palców, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider, Lewa Ręka, Płynność, Niezależność palców, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider, Zmiana Strun, Lewa Ręka, Picking, Pick Slanting, Niezależność palców, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shred, Alternate Picking, Skale, Synchronizacja, Lewa Ręka, Speed Burst, Niezależność palców, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shred, Alternate Picking, Skale, Synchronizacja, Lewa Ręka, Speed Burst, Zmienianie pozycji, Niezależność palców, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shred, Alternate Picking, Skale, Synchronizacja, Lewa Ręka, Speed Burst, Zmienianie Strun, Niezależność palców, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shred, Alternate Picking, Skale, Synchronizacja, Lewa Ręka, Speed Burst, Zmienianie Strun, Zmienianie pozycji, Zmienianie pozycji, Niezależność palców, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shred, Alternate Picking, Synchronizacja, Zmienianie pozycji, Zmienianie Strun, Shred, Płynność, Szybkość, Niezależność palców, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider, String Skipping, Synchronizacja, Lewa Ręka, Wprawki, Niezależność palców, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider, Alternate Picking, Pick Slanting, Synchronizacja, Pick Slanting, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rozciąganie, Siła, Zmienianie Strun, Niezależność palców, Lewa Ręka, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternate Picking, Szybkość, Płynność, Lewa Ręka, Zmienianie Strun, Niezależność palców, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternate Picking, Szybkość, Płynność, Lewa Ręka, Zmienianie Strun, Niezależność palców, Arpeggio, Shred, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweep Picking, Economy Picking, Szybkość, Płynność, Niezależność palców, Zmienianie Strun, Arpeggio, Shred, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternate Picking, Synchronizacja, Shred, Niezależność palców, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternate Picking, Zmienianie Strun, Rytm, Speed Burst, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternate Picking, Zmienianie pozycji, Zmienianie Strun, Synchronizacja, Płynność, Etiuda, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternate Picking, Synchronizacja, Zmienianie pozycji, Zmienianie Strun, Shred, Speed Burst, String Skipping, Rytm, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szybkość, Płynność, Lewa Ręka, Arpeggio, Akordy, </t>
   </si>
 </sst>
 </file>
@@ -1260,9 +1413,9 @@
   <sheetFormatPr defaultRowHeight="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" customWidth="1"/>
     <col min="3" max="3" width="7.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="37.85546875" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="54" customWidth="1"/>
   </cols>
@@ -1295,10 +1448,10 @@
         <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>63</v>
+        <v>309</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>31</v>
@@ -1315,10 +1468,10 @@
         <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>32</v>
@@ -1335,10 +1488,10 @@
         <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -1355,10 +1508,10 @@
         <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>34</v>
@@ -1375,7 +1528,7 @@
         <v>36</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>54</v>
@@ -1389,13 +1542,13 @@
     </row>
     <row r="7" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>62</v>
@@ -1415,10 +1568,10 @@
         <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>57</v>
@@ -1435,10 +1588,10 @@
         <v>39</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>58</v>
@@ -1455,10 +1608,10 @@
         <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>59</v>
@@ -1475,10 +1628,10 @@
         <v>39</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>60</v>
@@ -1495,13 +1648,13 @@
         <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>51</v>
@@ -1515,13 +1668,13 @@
         <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>52</v>
@@ -1535,13 +1688,13 @@
         <v>39</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>53</v>
@@ -1549,1080 +1702,1162 @@
     </row>
     <row r="15" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="F15" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>121</v>
+        <v>285</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>121</v>
+        <v>285</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>121</v>
+        <v>285</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>121</v>
+        <v>285</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>121</v>
+        <v>285</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>121</v>
+        <v>285</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>158</v>
+        <v>286</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>158</v>
+        <v>287</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>158</v>
+        <v>287</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>158</v>
+        <v>287</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>159</v>
+        <v>289</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>159</v>
+        <v>290</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>159</v>
+        <v>290</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>159</v>
+        <v>291</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>159</v>
+        <v>294</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>159</v>
+        <v>295</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>159</v>
+        <v>295</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>159</v>
+        <v>295</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>159</v>
+        <v>295</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>159</v>
+        <v>296</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>159</v>
+        <v>297</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>159</v>
+        <v>298</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E45" s="3"/>
+        <v>299</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>247</v>
+      </c>
       <c r="F45" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="9" t="s">
-        <v>190</v>
+        <v>240</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E47" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="F47" s="8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>186</v>
+        <v>243</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E48" s="3"/>
+        <v>292</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="F48" s="9" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>187</v>
+      <c r="A49" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>78</v>
+        <v>178</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" s="8" t="s">
-        <v>193</v>
+        <v>293</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>188</v>
+      <c r="A50" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C50" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="9" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" s="8" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
+      <c r="D52" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="9" t="s">
-        <v>196</v>
+      <c r="F52" s="8" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="E53" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="F53" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E54" s="3"/>
+        <v>257</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>256</v>
+      </c>
       <c r="F54" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F55" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E55" s="3"/>
-      <c r="F55" s="9" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E56" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>260</v>
+      </c>
       <c r="F56" s="8" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E57" s="3"/>
+        <v>263</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>262</v>
+      </c>
       <c r="F57" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E58" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>264</v>
+      </c>
       <c r="F58" s="8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E59" s="3"/>
+        <v>267</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="F59" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="D60" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E60" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>268</v>
+      </c>
       <c r="F60" s="8" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="F61" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E61" s="3"/>
-      <c r="F61" s="9" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="D62" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E62" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>270</v>
+      </c>
       <c r="F62" s="8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C63" s="3"/>
+        <v>208</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="D63" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E63" s="3"/>
+        <v>273</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>271</v>
+      </c>
       <c r="F63" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="D64" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="E64" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>272</v>
+      </c>
       <c r="F64" s="8" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C65" s="3"/>
+        <v>220</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="D65" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E65" s="3"/>
+        <v>302</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>277</v>
+      </c>
       <c r="F65" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F66" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" s="6" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C67" s="3"/>
+        <v>220</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="D67" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E67" s="3"/>
+        <v>304</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>279</v>
+      </c>
       <c r="F67" s="9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="D68" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E68" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>280</v>
+      </c>
       <c r="F68" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C69" s="3"/>
+        <v>220</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="D69" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E69" s="3"/>
+        <v>306</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>281</v>
+      </c>
       <c r="F69" s="9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="D70" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E70" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>282</v>
+      </c>
       <c r="F70" s="8" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C71" s="3"/>
+        <v>220</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="D71" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E71" s="3"/>
+        <v>308</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>283</v>
+      </c>
       <c r="F71" s="9" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E72" s="2"/>
+      <c r="E72" s="2" t="s">
+        <v>284</v>
+      </c>
       <c r="F72" s="8" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2733,9 +2968,10 @@
     <hyperlink ref="F17" r:id="rId8" xr:uid="{C020F178-7F0C-4255-84C0-D02096F78587}"/>
     <hyperlink ref="F19" r:id="rId9" xr:uid="{32919252-880A-47F2-A773-C93662E9BCDB}"/>
     <hyperlink ref="F66" r:id="rId10" xr:uid="{D2B6880C-A11D-476C-9E19-250564686AE4}"/>
+    <hyperlink ref="F46" r:id="rId11" xr:uid="{A8B4C01F-FFFA-442D-8753-183715E63934}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
 </worksheet>
 </file>
 

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[W SZPONACH GITARY]\HTML - ĆWICZENIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080F5A10-E3E3-45D0-8603-A9BB591576E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5531D3-ED9C-480C-AAEA-B2480F488570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="615" windowWidth="25095" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ćwiczenia" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="311">
   <si>
     <t>NAZWA</t>
   </si>
@@ -968,6 +968,9 @@
   </si>
   <si>
     <t xml:space="preserve">Szybkość, Płynność, Lewa Ręka, Arpeggio, Akordy, </t>
+  </si>
+  <si>
+    <t>DATA</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1049,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1069,12 +1072,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF2E2E2E"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF2E2E2E"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1104,6 +1118,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1409,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr defaultRowHeight="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1420,7 +1437,7 @@
     <col min="6" max="6" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1439,8 +1456,11 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G1" s="11" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -1460,7 +1480,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
@@ -1480,7 +1500,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
@@ -1500,7 +1520,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
@@ -1520,7 +1540,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>35</v>
       </c>
@@ -1540,7 +1560,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>74</v>
       </c>
@@ -1560,7 +1580,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -1580,7 +1600,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>41</v>
       </c>
@@ -1600,7 +1620,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>42</v>
       </c>
@@ -1620,7 +1640,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>43</v>
       </c>
@@ -1640,7 +1660,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>44</v>
       </c>
@@ -1660,7 +1680,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>45</v>
       </c>
@@ -1680,7 +1700,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>46</v>
       </c>
@@ -1700,7 +1720,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>78</v>
       </c>
@@ -1720,7 +1740,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>79</v>
       </c>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[W SZPONACH GITARY]\HTML - ĆWICZENIA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - ĆWICZENIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5531D3-ED9C-480C-AAEA-B2480F488570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E11639-92B4-4F3C-96DB-65094E8B4984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="615" windowWidth="25095" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26310" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ćwiczenia" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="326">
   <si>
     <t>NAZWA</t>
   </si>
@@ -971,6 +971,51 @@
   </si>
   <si>
     <t>DATA</t>
+  </si>
+  <si>
+    <t>RYTM - Wartości Regularne - 01 Cała Nuta</t>
+  </si>
+  <si>
+    <t>RYTM - Wartości Regularne - 02 Pół Nuta</t>
+  </si>
+  <si>
+    <t>RYTM - Wartości Regularne - 03 Ćwierćnuta</t>
+  </si>
+  <si>
+    <t>RYTM - Wartości Regularne - 04 Ósemka</t>
+  </si>
+  <si>
+    <t>RYTM - Wartości Regularne - 05 Szesnastka</t>
+  </si>
+  <si>
+    <t>RYTM - Wartości Regularne - 06 Trzydziestodwójka</t>
+  </si>
+  <si>
+    <t>PODSTAWOWY</t>
+  </si>
+  <si>
+    <t>Rytm, Wartości rytmiczne</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=13X-yluYLt_c5iqODtiHkaG-873Nc5ANl&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1X13u9YhIIObXHQIVLsTn35_uaXAubTPb&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1qND0Inj7NKE9Hvg5e-6Q3JtxwXFKg18O&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1UhxiNGx9oZCdhHkd0Efm3OU1_lyovwjh&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1HqQoAem6M1Q5fxQspalMGagXMuFNHh-C&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1rvMdbosTPbQKKunMm7nFPKtXP4Gk47sI&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>Nauka podstawowych wartości rytmicznych zrealizowanych na bazie rytmicznego zapisu nutowego.</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1133,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1123,6 +1168,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
@@ -2720,7 +2766,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>221</v>
       </c>
@@ -2740,7 +2786,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>223</v>
       </c>
@@ -2760,7 +2806,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>225</v>
       </c>
@@ -2780,7 +2826,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>227</v>
       </c>
@@ -2800,7 +2846,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>229</v>
       </c>
@@ -2820,7 +2866,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>231</v>
       </c>
@@ -2840,7 +2886,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>233</v>
       </c>
@@ -2860,7 +2906,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>236</v>
       </c>
@@ -2880,55 +2926,145 @@
         <v>237</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="9"/>
-    </row>
-    <row r="74" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="8"/>
-    </row>
-    <row r="75" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="9"/>
-    </row>
-    <row r="76" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="8"/>
-    </row>
-    <row r="77" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="9"/>
-    </row>
-    <row r="78" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="8"/>
-    </row>
-    <row r="79" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="G73" s="12">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="G74" s="12">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="G75" s="12">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="G76" s="12">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="G77" s="12">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="G78" s="12">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -2936,7 +3072,7 @@
       <c r="E79" s="3"/>
       <c r="F79" s="9"/>
     </row>
-    <row r="80" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - ĆWICZENIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E11639-92B4-4F3C-96DB-65094E8B4984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A89738-DD5F-4DC2-8E4B-DDB00C0F68BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26310" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ćwiczenia" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="363">
   <si>
     <t>NAZWA</t>
   </si>
@@ -1015,7 +1015,118 @@
     <t>https://drive.google.com/open?id=1rvMdbosTPbQKKunMm7nFPKtXP4Gk47sI&amp;usp=drive_fs</t>
   </si>
   <si>
-    <t>Nauka podstawowych wartości rytmicznych zrealizowanych na bazie rytmicznego zapisu nutowego.</t>
+    <t>RYTM - Wartości Nieregularne - 01 Triola Półnutowa</t>
+  </si>
+  <si>
+    <t>RYTM - Wartości Nieregularne - 02 Triola Ćwierćnutowa</t>
+  </si>
+  <si>
+    <t>RYTM - Wartości Nieregularne - 03 Triole Ósemkowe</t>
+  </si>
+  <si>
+    <t>RYTM - Wartości Nieregularne - 04 Kwintole</t>
+  </si>
+  <si>
+    <t>RYTM - Wartości Nieregularne - 05 Sekstole</t>
+  </si>
+  <si>
+    <t>RYTM - Wartości Nieregularne - 05 Triole Szesnastkowe</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1jHeupP6wOa38sUcZrG1rEM1wLULfhR8X&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1G-aV7FbK85sJMBwzWIxpxA2qqpD6LyfV&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1We6tjKIYzH26pJEQOKRw6Oht4xyEnGUY&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1daigRtpLh8DJ_ZrJOQLcp2B9sW69Q3GF&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1LRpOae_aVr-C6Tzf43DhLmTsvpN8qirF&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1oF6sFZzu7Sx5RqxmNaPlPzpM81O5Qd0g&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>Rytm, Wartości rytmiczne nieregularne</t>
+  </si>
+  <si>
+    <t>POCZĄTKUJĄCY - Ćwiczenia na synchronizacje dłoni</t>
+  </si>
+  <si>
+    <t>POCZĄTKUJĄCY - Ćwiczymy puste struny</t>
+  </si>
+  <si>
+    <t>POCZĄTKUJĄCY - Mieszamy puste struny z łapanymi progami</t>
+  </si>
+  <si>
+    <t>Zbiór 16 ćwiczeń dla początkujących na synchronizację obu dłoni.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1FbUc6TWj0LxyPMjBd8jRDEDXQGF8e67k&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1zJZqUZyN_Kk3K9zG02y4W1DKpqznnv-v&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1cLZBf_6SH_KX5YNWnSZb_GoemU_EyTZd&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>Zbiór 15 ćwiczeń dla początkujących na lepsze opanowanie prawej dłoni poprzez granie pustych strun.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zbiór 16 ćwiczeń dla początkujących </t>
+  </si>
+  <si>
+    <t>POCZĄTKUJĄCY</t>
+  </si>
+  <si>
+    <t>Synchronizacja, Prawa ręka, Kostkowanie, Granie palcami</t>
+  </si>
+  <si>
+    <t>Prawa ręka, puste struny,</t>
+  </si>
+  <si>
+    <t>Synchronizacja, Prawa ręka, Kostkowanie, Granie palcami, pojedyńcze dźwięki</t>
+  </si>
+  <si>
+    <t>Ćwiczenie rozwijające umiejętność rozpoznawania, liczenia i wykonywania całej nuty na podstawie zapisu nutowego.</t>
+  </si>
+  <si>
+    <t>Ćwiczenie rozwijające umiejętność rozpoznawania, liczenia i wykonywania półnuty na podstawie zapisu nutowego.</t>
+  </si>
+  <si>
+    <t>Ćwiczenie rozwijające umiejętność rozpoznawania, liczenia i wykonywania ćwierćnuty na podstawie zapisu nutowego.</t>
+  </si>
+  <si>
+    <t>Ćwiczenie rozwijające umiejętność rozpoznawania, liczenia i wykonywania ósemek na podstawie zapisu nutowego.</t>
+  </si>
+  <si>
+    <t>Ćwiczenie rozwijające umiejętność rozpoznawania, liczenia i wykonywania szesnastek na podstawie zapisu nutowego.</t>
+  </si>
+  <si>
+    <t>Ćwiczenie rozwijające umiejętność rozpoznawania, liczenia i wykonywania trzydziestodwójek na podstawie zapisu nutowego.</t>
+  </si>
+  <si>
+    <t>Ćwiczenie rozwijające umiejętność rozpoznawania, liczenia i wykonywania trioli półnutowych na podstawie zapisu nutowego.</t>
+  </si>
+  <si>
+    <t>Ćwiczenie rozwijające umiejętność rozpoznawania, liczenia i wykonywania trioli ćwierćnutowych na podstawie zapisu nutowego.</t>
+  </si>
+  <si>
+    <t>Ćwiczenie rozwijające umiejętność rozpoznawania, liczenia i wykonywania trioli ósemkowych na podstawie zapisu nutowego.</t>
+  </si>
+  <si>
+    <t>Ćwiczenie rozwijające umiejętność rozpoznawania, liczenia i wykonywania kwintoli na podstawie zapisu nutowego.</t>
+  </si>
+  <si>
+    <t>Ćwiczenie rozwijające umiejętność rozpoznawania, liczenia i wykonywania sekstoli na podstawie zapisu nutowego.</t>
+  </si>
+  <si>
+    <t>Ćwiczenie rozwijające umiejętność rozpoznawania, liczenia i wykonywania trioli szesnastkowych na podstawie zapisu nutowego.</t>
   </si>
 </sst>
 </file>
@@ -1472,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr defaultRowHeight="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -2940,7 +3051,7 @@
         <v>318</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>319</v>
@@ -2963,7 +3074,7 @@
         <v>318</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>320</v>
@@ -2986,7 +3097,7 @@
         <v>318</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>321</v>
@@ -3009,7 +3120,7 @@
         <v>318</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>325</v>
+        <v>354</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>322</v>
@@ -3032,7 +3143,7 @@
         <v>318</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>323</v>
@@ -3055,7 +3166,7 @@
         <v>318</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>324</v>
@@ -3065,52 +3176,338 @@
       </c>
     </row>
     <row r="79" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="9"/>
+      <c r="A79" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="G79" s="12">
+        <v>46239</v>
+      </c>
     </row>
     <row r="80" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="8"/>
-    </row>
-    <row r="81" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="9"/>
-    </row>
-    <row r="82" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="8"/>
-    </row>
-    <row r="83" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="9"/>
-    </row>
-    <row r="84" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="8"/>
+      <c r="A80" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="G80" s="12">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="G81" s="12">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="G82" s="12">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="G83" s="12">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="G84" s="12">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="8"/>
+    </row>
+    <row r="89" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="9"/>
+    </row>
+    <row r="90" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="8"/>
+    </row>
+    <row r="91" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="3"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="9"/>
+    </row>
+    <row r="92" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="8"/>
+    </row>
+    <row r="93" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="3"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="9"/>
+    </row>
+    <row r="94" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="8"/>
+    </row>
+    <row r="95" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="3"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="9"/>
+    </row>
+    <row r="96" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="8"/>
+    </row>
+    <row r="97" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="3"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="9"/>
+    </row>
+    <row r="98" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="8"/>
+    </row>
+    <row r="99" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="3"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="9"/>
+    </row>
+    <row r="100" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="8"/>
+    </row>
+    <row r="101" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="3"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="9"/>
+    </row>
+    <row r="102" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="8"/>
+    </row>
+    <row r="103" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="3"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="9"/>
+    </row>
+    <row r="104" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3125,9 +3522,10 @@
     <hyperlink ref="F19" r:id="rId9" xr:uid="{32919252-880A-47F2-A773-C93662E9BCDB}"/>
     <hyperlink ref="F66" r:id="rId10" xr:uid="{D2B6880C-A11D-476C-9E19-250564686AE4}"/>
     <hyperlink ref="F46" r:id="rId11" xr:uid="{A8B4C01F-FFFA-442D-8753-183715E63934}"/>
+    <hyperlink ref="F79" r:id="rId12" xr:uid="{39785A4B-CDEC-4B2F-B0E5-38757511CF9A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>
 

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - ĆWICZENIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A89738-DD5F-4DC2-8E4B-DDB00C0F68BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F761CEFC-5182-423E-AAC6-A6F5D5048D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="362">
   <si>
     <t>NAZWA</t>
   </si>
@@ -989,9 +989,6 @@
   </si>
   <si>
     <t>RYTM - Wartości Regularne - 06 Trzydziestodwójka</t>
-  </si>
-  <si>
-    <t>PODSTAWOWY</t>
   </si>
   <si>
     <t>Rytm, Wartości rytmiczne</t>
@@ -3045,16 +3042,16 @@
         <v>120</v>
       </c>
       <c r="C73" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F73" s="9" t="s">
         <v>318</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>319</v>
       </c>
       <c r="G73" s="12">
         <v>46238</v>
@@ -3068,16 +3065,16 @@
         <v>120</v>
       </c>
       <c r="C74" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="E74" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G74" s="12">
         <v>46238</v>
@@ -3091,16 +3088,16 @@
         <v>120</v>
       </c>
       <c r="C75" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>318</v>
-      </c>
       <c r="E75" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G75" s="12">
         <v>46238</v>
@@ -3114,16 +3111,16 @@
         <v>120</v>
       </c>
       <c r="C76" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="E76" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G76" s="12">
         <v>46238</v>
@@ -3137,16 +3134,16 @@
         <v>120</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>318</v>
-      </c>
       <c r="E77" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G77" s="12">
         <v>46238</v>
@@ -3160,16 +3157,16 @@
         <v>120</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="E78" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G78" s="12">
         <v>46238</v>
@@ -3177,22 +3174,22 @@
     </row>
     <row r="79" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G79" s="12">
         <v>46239</v>
@@ -3200,22 +3197,22 @@
     </row>
     <row r="80" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G80" s="12">
         <v>46239</v>
@@ -3223,22 +3220,22 @@
     </row>
     <row r="81" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G81" s="12">
         <v>46239</v>
@@ -3246,22 +3243,22 @@
     </row>
     <row r="82" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G82" s="12">
         <v>46239</v>
@@ -3269,22 +3266,22 @@
     </row>
     <row r="83" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G83" s="12">
         <v>46239</v>
@@ -3292,22 +3289,22 @@
     </row>
     <row r="84" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G84" s="12">
         <v>46239</v>
@@ -3315,62 +3312,62 @@
     </row>
     <row r="85" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B85" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="E85" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="F85" s="9" t="s">
         <v>341</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - ĆWICZENIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F761CEFC-5182-423E-AAC6-A6F5D5048D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C49B65-B6DB-417D-BC53-3FCBE010E067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13200" yWindow="-105" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ćwiczenia" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="439">
   <si>
     <t>NAZWA</t>
   </si>
@@ -1124,13 +1124,244 @@
   </si>
   <si>
     <t>Ćwiczenie rozwijające umiejętność rozpoznawania, liczenia i wykonywania trioli szesnastkowych na podstawie zapisu nutowego.</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 01A CAŁA NUTA - półnuta</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 03A ĆWIERĆNUTA - półnuta</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 03B ĆWIERĆNUTA - ósemka</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 03C ĆWIERĆNUTA - półnuta, ósemka</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 04A ÓSEMKA - ćwierćnuta</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 04C ÓSEMKA - triola ósemkowa</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 04B - Ósemki, ćwierćnuty i Półnuty</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 04D ÓSEMKA - szesnastka</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 04E ÓSEMKA - ćwierćnuta, triola ósemkowa</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 04F ÓSEMKA - ćwierćnuta, szesnastka</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 04G ÓSEMKA - triola ósemkowa, szesnastka</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 05A TRIOLA ÓSEMKOWA - ósemka</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 05B TRIOLA ÓSEMKOWA - szesnastka</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 05C TRIOLA ÓSEMKOWA - ósemka, szesnastka</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 06A SZESNASTKA - ósemka</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 06B SZESNASTKA - triola ósemkowa</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 06C SZESNASTKA - triola szesnastkowa</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 06D SZESNASTKA - ósemka, triola ósemkowa</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 06E SZESNASTKA - ósemka, triola szesnastkowa</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 06F SZESNASTKA - triola ósemkowa, triola szesnastkowa</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 07A TRIOLA SZESNASTKOWA - szesnastka</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 07B TRIOLA SZESNASTKOWA - szesnastka, triola ósemkowa</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 07C - Triola szesnastkowa, Ósemki i Szesnastki - GP</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1wLN3l2jzTSVix9MhTiszzQD5qARAoQxA&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1oMcEkrrAdbv58C4sFPcBFKzZ0Oa-t-qN&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 02B PÓŁNUTA - cała nuta, ćwierćnuta</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1PnSzjSOakGjgJrch-Xz-LdKg1QhzbFIG&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1bO5qXJV69Cvi1kiYPAi7TSaDJkmcmLok&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1iW_bWDdsKfZnBTq4qmW_kti2blBYQUIp&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=15tItK6IMUoWptUP0kMChU8mCGTITmsXB&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1kupcrM-eAwb_OuC7ej4OW17nEBnsEXJn&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=11ydmK50jWazzt3veEjHLmchBlP32V4kv&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=122Esasg3OlDa8rdyItGe7RwuqMwoz5Ut&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>Nauczysz się utrzymywać puls podczas grania długich wartości oraz precyzyjnie przechodzić między całą nutą a półnutami. Opanujesz kontrolowanie długości wybrzmiewania dźwięków.</t>
+  </si>
+  <si>
+    <t>Nauczysz się dzielić półnutę na krótsze wartości i zachowywać stabilny puls podczas zmian rytmicznych. Opanujesz dokładne wejścia na kolejne części taktu.</t>
+  </si>
+  <si>
+    <t>Nauczysz się płynnie łączyć całą nutę, półnuty i ćwierćnuty. Opanujesz swobodne przechodzenie między długimi i krótkimi wartościami rytmicznymi.</t>
+  </si>
+  <si>
+    <t>Nauczysz się wydłużać dźwięki przy zachowaniu wewnętrznego pulsu ćwierćnutowego. Opanujesz precyzyjne rozpoczynanie i kończenie półnut.</t>
+  </si>
+  <si>
+    <t>Nauczysz się przechodzić między ćwierćnutami i ósemkami. Opanujesz liczenie z wykorzystaniem „i” oraz równomierne wykonywanie ósemek.</t>
+  </si>
+  <si>
+    <t>Nauczysz się łączyć półnuty, ćwierćnuty i ósemki w jednym przebiegu. Opanujesz płynne zmiany gęstości rytmu bez utraty pulsu.</t>
+  </si>
+  <si>
+    <t>Nauczysz się swobodnie przechodzić między ósemkami i ćwierćnutami. Opanujesz utrzymywanie równego podziału ósemkowego również podczas dłuższych wartości.</t>
+  </si>
+  <si>
+    <t>Nauczysz się odnajdywać puls po pauzach oraz łączyć półnuty, ćwierćnuty i ósemki w bardziej wymagających układach rytmicznych.</t>
+  </si>
+  <si>
+    <t>Nauczysz się zmieniać podział z dwójkowego na trójkowy. Opanujesz płynne przechodzenie między ósemkami i triolami ósemkowymi.</t>
+  </si>
+  <si>
+    <t>Nauczysz się przechodzić między ósemkami i szesnastkami. Opanujesz kontrolowanie zmian gęstości rytmu oraz równomierne granie szybszych wartości.</t>
+  </si>
+  <si>
+    <t>Nauczysz się łączyć ćwierćnuty, ósemki i triole ósemkowe. Opanujesz zmianę sposobu liczenia bez gubienia pulsu.</t>
+  </si>
+  <si>
+    <t>Nauczysz się łączyć ćwierćnuty, ósemki i szesnastki. Opanujesz szybkie przechodzenie między trzema poziomami gęstości rytmu.</t>
+  </si>
+  <si>
+    <t>Nauczysz się przechodzić między ósemkami, triolami ósemkowymi i szesnastkami. Opanujesz rozpoznawanie i wykonywanie różnych podziałów rytmicznych.</t>
+  </si>
+  <si>
+    <t>Nauczysz się świadomie zmieniać podział trójkowy na dwójkowy. Opanujesz zachowanie tego samego pulsu mimo zmiany liczby dźwięków.</t>
+  </si>
+  <si>
+    <t>Nauczysz się przechodzić między triolami ósemkowymi i szesnastkami. Opanujesz precyzyjne zmiany podziału rytmicznego.</t>
+  </si>
+  <si>
+    <t>Nauczysz się swobodnie poruszać między ósemkami, triolami ósemkowymi i szesnastkami. Opanujesz utrzymywanie wspólnego pulsu dla różnych podziałów.</t>
+  </si>
+  <si>
+    <t>Nauczysz się rozrzedzać rytm z szesnastek do ósemek i ponownie wracać do szybszych wartości. Opanujesz równomierne wykonywanie szesnastek.</t>
+  </si>
+  <si>
+    <t>Nauczysz się przechodzić między szesnastkami i triolami ósemkowymi. Opanujesz zmianę podziału dwójkowego na trójkowy bez utraty tempa.</t>
+  </si>
+  <si>
+    <t>Nauczysz się przechodzić między szesnastkami i triolami szesnastkowymi. Opanujesz wykonywanie bardzo gęstych podziałów rytmicznych.</t>
+  </si>
+  <si>
+    <t>Nauczysz się łączyć ósemki, triole ósemkowe i szesnastki. Opanujesz szybkie zmiany podziałów rytmicznych w jednym ćwiczeniu.</t>
+  </si>
+  <si>
+    <t>Nauczysz się łączyć ósemki, szesnastki i triole szesnastkowe. Opanujesz kontrolowanie dużych zmian gęstości rytmu.</t>
+  </si>
+  <si>
+    <t>Nauczysz się łączyć triole ósemkowe, szesnastki i triole szesnastkowe. Opanujesz najbardziej wymagające zmiany podziałów rytmicznych.</t>
+  </si>
+  <si>
+    <t>Nauczysz się przechodzić między triolami szesnastkowymi i szesnastkami. Opanujesz równomierne wykonywanie bardzo szybkich podziałów.</t>
+  </si>
+  <si>
+    <t>Nauczysz się łączyć triole szesnastkowe, szesnastki i triole ósemkowe. Opanujesz płynne przechodzenie między różnymi rodzajami triol.</t>
+  </si>
+  <si>
+    <t>Nauczysz się swobodnie przechodzić między ósemkami, szesnastkami i triolami szesnastkowymi. Opanujesz najbardziej wymagające kombinacje podziałów rytmicznych.</t>
+  </si>
+  <si>
+    <t>Rytm, Wartości rytmiczne,</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=13SYTHurBrzFRxHj8_qTiUF8Abxu3BEJd&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1LBS7iS3afU2v47CHuofYLRV15OP2vvoa&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1bFn03eVyzw6FHbO7w2V3XpCI-ig9WWbm&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1no_XGX4AZgW4fdL4x6PEfaO-9cfT2T-c&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1K0YQW5MCj14HaHsg5eKg1S_gT2hShfmf&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1DSaR3b406dEfJcTeTJuh-bOLp2h_qAQY&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1xsiS4G3SMDBoNnLuxEyN_K17CLissmUl&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1UP5uTcsCphBuCmIOxZBA-XqCkq5hTgAN&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1_TilYSKkcRKbf6_s41eXQ83A2EQzxmXM&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>RYTM - MIESZAMY WARTOŚCI - 02A - Całe nuty, Półnuty i Pauzy</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1lIBmFh3KsdBKwIjWeAWtKN0EsMayHuQ1&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=14Hnk6x6eRKLEx8olwP6HPJhJac16Xr0u&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1AeKcYARW2-u1XHf4Mx_oePbECOqE2c-E&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>EXPERT</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1IDvK5KlcBvpSGeeXteHUf6Wt_2d5xzYe&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Xt156WD824hF1Fy3T7FsIkyrX8f27PO9&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1YI6lBX0_KATfhPSqiNBS4_ZdiWxi1RI5&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ytfKaunM52Y8Pc-lL5chqGrlv2uWVM7d&amp;usp=drive_fs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1142,11 +1373,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFC8A84B"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFF0ECE0"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1163,23 +1389,43 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFC8A84B"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1188,21 +1434,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1A1A1A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF141414"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF0F0F0F"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1236,53 +1472,373 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF2E2E2E"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF2E2E2E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF2E2E2E"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF2E2E2E"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF2E2E2E"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF2E2E2E"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF2E2E2E"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF2E2E2E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF2E2E2E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF2E2E2E"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF2E2E2E"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF2E2E2E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF2E2E2E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF2E2E2E"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF2E2E2E"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF2E2E2E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF2E2E2E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF2E2E2E"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF2E2E2E"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF2E2E2E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF2E2E2E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF2E2E2E"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF2E2E2E"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF2E2E2E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF2E2E2E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF2E2E2E"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF2E2E2E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF2E2E2E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF2E2E2E"/>
+        </left>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1293,6 +1849,22 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C07D3C02-8874-42BA-9F17-527B00E3E1FE}" name="Tabela5" displayName="Tabela5" ref="A1:G112" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" tableBorderDxfId="9">
+  <autoFilter ref="A1:G112" xr:uid="{C07D3C02-8874-42BA-9F17-527B00E3E1FE}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{E6AF589C-AA5A-4A47-BCF7-B59D18AF558A}" name="NAZWA" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{0DEB36FC-91F5-42CF-AB13-670423C77CBA}" name="KATEGORIA" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{3BA5E285-C36D-4180-B040-6E23ADF59AAF}" name="POZIOM" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{AB92F723-7972-4F28-80B6-5B8CB0B682C3}" name="TAGI" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{B91D9D24-B508-4D52-8F85-961D14EF005E}" name="OPIS" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{925457DF-C897-4E23-9CBE-5566E9A6DD01}" name="LINK" dataDxfId="3" dataCellStyle="Hiperłącze"/>
+    <tableColumn id="7" xr3:uid="{AE553085-8794-4B4C-BD9D-95D8C32A0655}" name="DATA" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1580,1931 +2152,2444 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr defaultRowHeight="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" customWidth="1"/>
     <col min="4" max="4" width="37.85546875" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="54" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="5" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="8" t="s">
         <v>24</v>
       </c>
+      <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>25</v>
       </c>
+      <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>26</v>
       </c>
+      <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>27</v>
       </c>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="8" t="s">
         <v>37</v>
       </c>
+      <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="8" t="s">
         <v>47</v>
       </c>
+      <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>48</v>
       </c>
+      <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="8" t="s">
         <v>49</v>
       </c>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="8" t="s">
         <v>50</v>
       </c>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="8" t="s">
         <v>51</v>
       </c>
+      <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="8" t="s">
         <v>52</v>
       </c>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="8" t="s">
         <v>53</v>
       </c>
+      <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="8" t="s">
         <v>85</v>
       </c>
+      <c r="G15" s="9"/>
     </row>
     <row r="16" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="8" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="G16" s="9"/>
+    </row>
+    <row r="17" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="8" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="G17" s="9"/>
+    </row>
+    <row r="18" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="8" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="G18" s="9"/>
+    </row>
+    <row r="19" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="8" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="G19" s="9"/>
+    </row>
+    <row r="20" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="10" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="G20" s="9"/>
+    </row>
+    <row r="21" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="10" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="G21" s="9"/>
+    </row>
+    <row r="22" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="10" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="G22" s="9"/>
+    </row>
+    <row r="23" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="10" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="G23" s="9"/>
+    </row>
+    <row r="24" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="10" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="G24" s="9"/>
+    </row>
+    <row r="25" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="10" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="G25" s="9"/>
+    </row>
+    <row r="26" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="10" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="G26" s="9"/>
+    </row>
+    <row r="27" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="10" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="G27" s="9"/>
+    </row>
+    <row r="28" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="10" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="G28" s="9"/>
+    </row>
+    <row r="29" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="10" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="G29" s="9"/>
+    </row>
+    <row r="30" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="10" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="G30" s="9"/>
+    </row>
+    <row r="31" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="10" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="G31" s="9"/>
+    </row>
+    <row r="32" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="10" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="G32" s="9"/>
+    </row>
+    <row r="33" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="10" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="G33" s="9"/>
+    </row>
+    <row r="34" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="10" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="10" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="G35" s="9"/>
+    </row>
+    <row r="36" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="F36" s="10" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+      <c r="G36" s="9"/>
+    </row>
+    <row r="37" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="F37" s="10" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+      <c r="G37" s="9"/>
+    </row>
+    <row r="38" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="10" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
+      <c r="G38" s="9"/>
+    </row>
+    <row r="39" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="10" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="G39" s="9"/>
+    </row>
+    <row r="40" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="10" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
+      <c r="G40" s="9"/>
+    </row>
+    <row r="41" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="10" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+      <c r="G41" s="9"/>
+    </row>
+    <row r="42" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="10" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="G42" s="9"/>
+    </row>
+    <row r="43" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F43" s="10" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+      <c r="G43" s="9"/>
+    </row>
+    <row r="44" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="F44" s="10" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+      <c r="G44" s="9"/>
+    </row>
+    <row r="45" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F45" s="10" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="G45" s="9"/>
+    </row>
+    <row r="46" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="8" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
+      <c r="G46" s="9"/>
+    </row>
+    <row r="47" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="10" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+      <c r="G47" s="9"/>
+    </row>
+    <row r="48" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="F48" s="10" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
+      <c r="G48" s="9"/>
+    </row>
+    <row r="49" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="F49" s="10" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="G49" s="9"/>
+    </row>
+    <row r="50" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="F50" s="10" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
+      <c r="G50" s="9"/>
+    </row>
+    <row r="51" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F51" s="10" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+      <c r="G51" s="9"/>
+    </row>
+    <row r="52" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="F52" s="10" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+      <c r="G52" s="9"/>
+    </row>
+    <row r="53" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="F53" s="8" t="s">
+      <c r="F53" s="10" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
+      <c r="G53" s="9"/>
+    </row>
+    <row r="54" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="F54" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
+      <c r="G54" s="9"/>
+    </row>
+    <row r="55" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="F55" s="10" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
+      <c r="G55" s="9"/>
+    </row>
+    <row r="56" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="F56" s="8" t="s">
+      <c r="F56" s="10" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
+      <c r="G56" s="9"/>
+    </row>
+    <row r="57" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" s="10" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
+      <c r="G57" s="9"/>
+    </row>
+    <row r="58" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="F58" s="8" t="s">
+      <c r="F58" s="10" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
+      <c r="G58" s="9"/>
+    </row>
+    <row r="59" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="E59" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="F59" s="9" t="s">
+      <c r="F59" s="10" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
+      <c r="G59" s="9"/>
+    </row>
+    <row r="60" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E60" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="F60" s="8" t="s">
+      <c r="F60" s="10" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
+      <c r="G60" s="9"/>
+    </row>
+    <row r="61" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="E61" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="F61" s="10" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
+      <c r="G61" s="9"/>
+    </row>
+    <row r="62" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E62" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="F62" s="8" t="s">
+      <c r="F62" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
+      <c r="G62" s="9"/>
+    </row>
+    <row r="63" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="F63" s="9" t="s">
+      <c r="F63" s="10" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
+      <c r="G63" s="9"/>
+    </row>
+    <row r="64" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="E64" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="F64" s="8" t="s">
+      <c r="F64" s="10" t="s">
         <v>219</v>
       </c>
+      <c r="G64" s="9"/>
     </row>
     <row r="65" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="F65" s="9" t="s">
+      <c r="F65" s="10" t="s">
         <v>222</v>
       </c>
+      <c r="G65" s="9"/>
     </row>
     <row r="66" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G66" s="9"/>
+    </row>
+    <row r="67" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C67" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B67" s="3" t="s">
+      <c r="D67" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="G67" s="9"/>
+    </row>
+    <row r="68" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B68" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C68" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="G68" s="9"/>
+    </row>
+    <row r="69" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B68" s="3" t="s">
+      <c r="D69" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="G69" s="9"/>
+    </row>
+    <row r="70" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B70" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C70" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B69" s="3" t="s">
+      <c r="D70" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="G70" s="9"/>
+    </row>
+    <row r="71" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B71" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C71" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="G71" s="9"/>
+    </row>
+    <row r="72" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C72" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C70" s="2" t="s">
+      <c r="D72" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="G72" s="9"/>
+    </row>
+    <row r="73" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="G73" s="11">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="G74" s="11">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="G75" s="11">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="G76" s="11">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="G77" s="11">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="G78" s="11">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C79" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C71" s="2" t="s">
+      <c r="D79" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="G79" s="11">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="G80" s="11">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="G81" s="11">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="G82" s="11">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C83" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C72" s="2" t="s">
+      <c r="D83" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="G83" s="11">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C84" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="B73" s="2" t="s">
+      <c r="D84" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="G84" s="11">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="G85" s="9"/>
+    </row>
+    <row r="86" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="G86" s="9"/>
+    </row>
+    <row r="87" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="G87" s="9"/>
+    </row>
+    <row r="88" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B88" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C88" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="G73" s="12">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B74" s="2" t="s">
+      <c r="D88" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="G88" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="B89" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C89" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="G74" s="12">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="B75" s="2" t="s">
+      <c r="D89" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="G89" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="B90" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C90" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="G75" s="12">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B76" s="2" t="s">
+      <c r="D90" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="G90" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="B91" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C91" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="G76" s="12">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B77" s="2" t="s">
+      <c r="D91" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="G91" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="B92" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C92" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G77" s="12">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="B78" s="2" t="s">
+      <c r="D92" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="G92" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="B93" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C93" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G78" s="12">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B79" s="2" t="s">
+      <c r="D93" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="G93" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B94" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C94" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="G79" s="12">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B80" s="2" t="s">
+      <c r="D94" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="G94" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="B95" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C95" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="D80" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="G80" s="12">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B81" s="2" t="s">
+      <c r="D95" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="G95" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="B96" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="G81" s="12">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B82" s="2" t="s">
+      <c r="C96" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="G96" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B97" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="G82" s="12">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B83" s="2" t="s">
+      <c r="C97" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="G97" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B98" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="G83" s="12">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="B84" s="2" t="s">
+      <c r="C98" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="G98" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="B99" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G84" s="12">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="8"/>
-    </row>
-    <row r="89" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="3"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="9"/>
-    </row>
-    <row r="90" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="8"/>
-    </row>
-    <row r="91" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="3"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="9"/>
-    </row>
-    <row r="92" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="8"/>
-    </row>
-    <row r="93" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="3"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="3"/>
-      <c r="F93" s="9"/>
-    </row>
-    <row r="94" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="8"/>
-    </row>
-    <row r="95" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="3"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="9"/>
-    </row>
-    <row r="96" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="8"/>
-    </row>
-    <row r="97" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="3"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="9"/>
-    </row>
-    <row r="98" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="8"/>
-    </row>
-    <row r="99" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="3"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="9"/>
-    </row>
-    <row r="100" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="8"/>
-    </row>
-    <row r="101" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="3"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="3"/>
-      <c r="F101" s="9"/>
-    </row>
-    <row r="102" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="8"/>
-    </row>
-    <row r="103" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="3"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="9"/>
-    </row>
-    <row r="104" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="8"/>
+      <c r="C99" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="G99" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="G100" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="G101" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="G102" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="G103" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="F104" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="G104" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F105" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="G105" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="F106" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="G106" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="G107" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="F108" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="G108" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="F109" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="G109" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="F110" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="G110" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="F111" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="G111" s="11">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="F112" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="G112" s="11">
+        <v>46240</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3520,9 +4605,13 @@
     <hyperlink ref="F66" r:id="rId10" xr:uid="{D2B6880C-A11D-476C-9E19-250564686AE4}"/>
     <hyperlink ref="F46" r:id="rId11" xr:uid="{A8B4C01F-FFFA-442D-8753-183715E63934}"/>
     <hyperlink ref="F79" r:id="rId12" xr:uid="{39785A4B-CDEC-4B2F-B0E5-38757511CF9A}"/>
+    <hyperlink ref="F111" r:id="rId13" xr:uid="{E2B870FB-FA48-41D9-B847-668BA958EB53}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
+  <tableParts count="1">
+    <tablePart r:id="rId15"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -3535,88 +4624,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
+      <c r="A2" s="2"/>
     </row>
     <row r="3" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
+      <c r="A11" s="2"/>
     </row>
     <row r="12" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
     </row>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - ĆWICZENIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C49B65-B6DB-417D-BC53-3FCBE010E067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BFF9E5-5C64-4527-B651-78D4F7B30104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13200" yWindow="-105" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ćwiczenia" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="454">
   <si>
     <t>NAZWA</t>
   </si>
@@ -1355,13 +1355,58 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1ytfKaunM52Y8Pc-lL5chqGrlv2uWVM7d&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://youtu.be/X2AvHdVcFBg?si=cG10RNIQDAFIMOxa</t>
+  </si>
+  <si>
+    <t>https://youtu.be/s6_liv4mL1g?si=obfYGsgfsE2IJA2T</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sTD2aJsM-tA?si=vgEW2tOxbYZyhT8b</t>
+  </si>
+  <si>
+    <t>https://youtu.be/KIfml7M1s4o?si=i3l2bFpBQCLqpwTO</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Q0Ogb6TchEs?si=xMHVIhdorGmrU0ug</t>
+  </si>
+  <si>
+    <t>YT</t>
+  </si>
+  <si>
+    <t>https://youtu.be/l-srstET1DQ?si=JyFKdZz16ELuc5Ro</t>
+  </si>
+  <si>
+    <t>https://youtu.be/B2hudMryKhU?si=N89P7UKVBSmHL9x-</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UsHyEi6tdXI?si=wiTAIceZWKCvI6zM</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-zkjiVzygQI?si=7-lBNOvzQcHifIiu</t>
+  </si>
+  <si>
+    <t>String Skipping, Alternate Picking, Selwencje skal, pickslanting.</t>
+  </si>
+  <si>
+    <t>To ćwiczenie nauczy Cię pokonywać niemalże niemożliwe kombinacje zmiany strun. Rozwiązaniem jest zmiana strun za pomocą pochylania płaszczyzny kostkowania.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0mj3jH8bCxM?si=7H5Wx7duZrSuDAzK</t>
+  </si>
+  <si>
+    <t>STRING SKIPPING - Sekwencja Penta5</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Nb-BfXzdX7U?si=6-PedbFAR3YJA2_l</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1424,6 +1469,32 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1438,7 +1509,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1485,12 +1556,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF2E2E2E"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF2E2E2E"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF2E2E2E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF2E2E2E"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF2E2E2E"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF2E2E2E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1524,12 +1621,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
     <dxf>
       <font>
         <b val="0"/>
@@ -1553,39 +1672,19 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF2E2E2E"/>
         </left>
         <right style="thin">
           <color rgb="FF2E2E2E"/>
         </right>
-        <top/>
-        <bottom/>
+        <top style="thin">
+          <color rgb="FF2E2E2E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF2E2E2E"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1838,6 +1937,64 @@
         </left>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF2E2E2E"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF2E2E2E"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1852,16 +2009,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C07D3C02-8874-42BA-9F17-527B00E3E1FE}" name="Tabela5" displayName="Tabela5" ref="A1:G112" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" tableBorderDxfId="9">
-  <autoFilter ref="A1:G112" xr:uid="{C07D3C02-8874-42BA-9F17-527B00E3E1FE}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E6AF589C-AA5A-4A47-BCF7-B59D18AF558A}" name="NAZWA" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{0DEB36FC-91F5-42CF-AB13-670423C77CBA}" name="KATEGORIA" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{3BA5E285-C36D-4180-B040-6E23ADF59AAF}" name="POZIOM" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{AB92F723-7972-4F28-80B6-5B8CB0B682C3}" name="TAGI" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{B91D9D24-B508-4D52-8F85-961D14EF005E}" name="OPIS" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{925457DF-C897-4E23-9CBE-5566E9A6DD01}" name="LINK" dataDxfId="3" dataCellStyle="Hiperłącze"/>
-    <tableColumn id="7" xr3:uid="{AE553085-8794-4B4C-BD9D-95D8C32A0655}" name="DATA" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C07D3C02-8874-42BA-9F17-527B00E3E1FE}" name="Tabela5" displayName="Tabela5" ref="A1:H113" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" tableBorderDxfId="8">
+  <autoFilter ref="A1:H113" xr:uid="{C07D3C02-8874-42BA-9F17-527B00E3E1FE}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{E6AF589C-AA5A-4A47-BCF7-B59D18AF558A}" name="NAZWA" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{0DEB36FC-91F5-42CF-AB13-670423C77CBA}" name="KATEGORIA" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{3BA5E285-C36D-4180-B040-6E23ADF59AAF}" name="POZIOM" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{AB92F723-7972-4F28-80B6-5B8CB0B682C3}" name="TAGI" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{B91D9D24-B508-4D52-8F85-961D14EF005E}" name="OPIS" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{925457DF-C897-4E23-9CBE-5566E9A6DD01}" name="LINK" dataDxfId="2" dataCellStyle="Hiperłącze"/>
+    <tableColumn id="7" xr3:uid="{AE553085-8794-4B4C-BD9D-95D8C32A0655}" name="DATA" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{43D57DCD-A736-4A4B-BF6D-A0034A15C252}" name="YT" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2152,7 +2310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr defaultRowHeight="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -2161,9 +2319,11 @@
     <col min="4" max="4" width="37.85546875" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="54" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="51.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2185,8 +2345,11 @@
       <c r="G1" s="5" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="16" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>22</v>
       </c>
@@ -2206,8 +2369,9 @@
         <v>24</v>
       </c>
       <c r="G2" s="9"/>
-    </row>
-    <row r="3" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H2" s="14"/>
+    </row>
+    <row r="3" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>28</v>
       </c>
@@ -2227,8 +2391,9 @@
         <v>25</v>
       </c>
       <c r="G3" s="9"/>
-    </row>
-    <row r="4" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H3" s="13"/>
+    </row>
+    <row r="4" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>29</v>
       </c>
@@ -2248,8 +2413,9 @@
         <v>26</v>
       </c>
       <c r="G4" s="9"/>
-    </row>
-    <row r="5" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H4" s="13"/>
+    </row>
+    <row r="5" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>30</v>
       </c>
@@ -2269,8 +2435,9 @@
         <v>27</v>
       </c>
       <c r="G5" s="9"/>
-    </row>
-    <row r="6" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="13"/>
+    </row>
+    <row r="6" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>35</v>
       </c>
@@ -2290,8 +2457,9 @@
         <v>37</v>
       </c>
       <c r="G6" s="9"/>
-    </row>
-    <row r="7" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H6" s="13"/>
+    </row>
+    <row r="7" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>74</v>
       </c>
@@ -2311,8 +2479,9 @@
         <v>38</v>
       </c>
       <c r="G7" s="9"/>
-    </row>
-    <row r="8" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="13"/>
+    </row>
+    <row r="8" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>40</v>
       </c>
@@ -2332,8 +2501,9 @@
         <v>47</v>
       </c>
       <c r="G8" s="9"/>
-    </row>
-    <row r="9" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H8" s="13"/>
+    </row>
+    <row r="9" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>41</v>
       </c>
@@ -2353,8 +2523,9 @@
         <v>48</v>
       </c>
       <c r="G9" s="9"/>
-    </row>
-    <row r="10" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H9" s="13"/>
+    </row>
+    <row r="10" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>42</v>
       </c>
@@ -2374,8 +2545,9 @@
         <v>49</v>
       </c>
       <c r="G10" s="9"/>
-    </row>
-    <row r="11" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H10" s="13"/>
+    </row>
+    <row r="11" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>43</v>
       </c>
@@ -2395,8 +2567,9 @@
         <v>50</v>
       </c>
       <c r="G11" s="9"/>
-    </row>
-    <row r="12" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H11" s="13"/>
+    </row>
+    <row r="12" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>44</v>
       </c>
@@ -2416,8 +2589,9 @@
         <v>51</v>
       </c>
       <c r="G12" s="9"/>
-    </row>
-    <row r="13" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H12" s="13"/>
+    </row>
+    <row r="13" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>45</v>
       </c>
@@ -2437,8 +2611,9 @@
         <v>52</v>
       </c>
       <c r="G13" s="9"/>
-    </row>
-    <row r="14" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H13" s="13"/>
+    </row>
+    <row r="14" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>46</v>
       </c>
@@ -2458,8 +2633,9 @@
         <v>53</v>
       </c>
       <c r="G14" s="9"/>
-    </row>
-    <row r="15" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H14" s="13"/>
+    </row>
+    <row r="15" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>78</v>
       </c>
@@ -2479,8 +2655,9 @@
         <v>85</v>
       </c>
       <c r="G15" s="9"/>
-    </row>
-    <row r="16" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H15" s="13"/>
+    </row>
+    <row r="16" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>79</v>
       </c>
@@ -2500,8 +2677,11 @@
         <v>86</v>
       </c>
       <c r="G16" s="9"/>
-    </row>
-    <row r="17" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H16" s="13" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>80</v>
       </c>
@@ -2521,8 +2701,9 @@
         <v>87</v>
       </c>
       <c r="G17" s="9"/>
-    </row>
-    <row r="18" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H17" s="13"/>
+    </row>
+    <row r="18" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>81</v>
       </c>
@@ -2542,8 +2723,9 @@
         <v>88</v>
       </c>
       <c r="G18" s="9"/>
-    </row>
-    <row r="19" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H18" s="13"/>
+    </row>
+    <row r="19" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>82</v>
       </c>
@@ -2563,8 +2745,9 @@
         <v>89</v>
       </c>
       <c r="G19" s="9"/>
-    </row>
-    <row r="20" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H19" s="13"/>
+    </row>
+    <row r="20" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>83</v>
       </c>
@@ -2584,8 +2767,9 @@
         <v>90</v>
       </c>
       <c r="G20" s="9"/>
-    </row>
-    <row r="21" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H20" s="13"/>
+    </row>
+    <row r="21" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>84</v>
       </c>
@@ -2605,8 +2789,9 @@
         <v>91</v>
       </c>
       <c r="G21" s="9"/>
-    </row>
-    <row r="22" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H21" s="13"/>
+    </row>
+    <row r="22" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>107</v>
       </c>
@@ -2626,8 +2811,11 @@
         <v>113</v>
       </c>
       <c r="G22" s="9"/>
-    </row>
-    <row r="23" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H22" s="13" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>108</v>
       </c>
@@ -2647,8 +2835,11 @@
         <v>114</v>
       </c>
       <c r="G23" s="9"/>
-    </row>
-    <row r="24" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H23" s="13" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>109</v>
       </c>
@@ -2668,8 +2859,11 @@
         <v>115</v>
       </c>
       <c r="G24" s="9"/>
-    </row>
-    <row r="25" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H24" s="13" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>110</v>
       </c>
@@ -2689,8 +2883,11 @@
         <v>116</v>
       </c>
       <c r="G25" s="9"/>
-    </row>
-    <row r="26" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H25" s="12" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>111</v>
       </c>
@@ -2710,8 +2907,9 @@
         <v>117</v>
       </c>
       <c r="G26" s="9"/>
-    </row>
-    <row r="27" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H26" s="13"/>
+    </row>
+    <row r="27" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>112</v>
       </c>
@@ -2731,8 +2929,9 @@
         <v>118</v>
       </c>
       <c r="G27" s="9"/>
-    </row>
-    <row r="28" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H27" s="13"/>
+    </row>
+    <row r="28" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>121</v>
       </c>
@@ -2752,8 +2951,11 @@
         <v>125</v>
       </c>
       <c r="G28" s="9"/>
-    </row>
-    <row r="29" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H28" s="13" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>122</v>
       </c>
@@ -2773,8 +2975,9 @@
         <v>126</v>
       </c>
       <c r="G29" s="9"/>
-    </row>
-    <row r="30" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H29" s="13"/>
+    </row>
+    <row r="30" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>123</v>
       </c>
@@ -2794,8 +2997,9 @@
         <v>127</v>
       </c>
       <c r="G30" s="9"/>
-    </row>
-    <row r="31" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H30" s="13"/>
+    </row>
+    <row r="31" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>124</v>
       </c>
@@ -2815,8 +3019,9 @@
         <v>128</v>
       </c>
       <c r="G31" s="9"/>
-    </row>
-    <row r="32" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H31" s="13"/>
+    </row>
+    <row r="32" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>130</v>
       </c>
@@ -2836,8 +3041,9 @@
         <v>131</v>
       </c>
       <c r="G32" s="9"/>
-    </row>
-    <row r="33" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H32" s="13"/>
+    </row>
+    <row r="33" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>132</v>
       </c>
@@ -2857,8 +3063,9 @@
         <v>133</v>
       </c>
       <c r="G33" s="9"/>
-    </row>
-    <row r="34" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H33" s="13"/>
+    </row>
+    <row r="34" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>134</v>
       </c>
@@ -2878,8 +3085,9 @@
         <v>135</v>
       </c>
       <c r="G34" s="9"/>
-    </row>
-    <row r="35" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H34" s="13"/>
+    </row>
+    <row r="35" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>136</v>
       </c>
@@ -2899,8 +3107,11 @@
         <v>137</v>
       </c>
       <c r="G35" s="9"/>
-    </row>
-    <row r="36" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H35" s="12" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>138</v>
       </c>
@@ -2916,12 +3127,15 @@
       <c r="E36" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="F36" s="10" t="s">
+      <c r="F36" s="12" t="s">
         <v>139</v>
       </c>
       <c r="G36" s="9"/>
-    </row>
-    <row r="37" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H36" s="13" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>140</v>
       </c>
@@ -2941,8 +3155,11 @@
         <v>141</v>
       </c>
       <c r="G37" s="9"/>
-    </row>
-    <row r="38" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H37" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>148</v>
       </c>
@@ -2962,8 +3179,9 @@
         <v>152</v>
       </c>
       <c r="G38" s="9"/>
-    </row>
-    <row r="39" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H38" s="13"/>
+    </row>
+    <row r="39" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>149</v>
       </c>
@@ -2983,8 +3201,9 @@
         <v>153</v>
       </c>
       <c r="G39" s="9"/>
-    </row>
-    <row r="40" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H39" s="13"/>
+    </row>
+    <row r="40" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>150</v>
       </c>
@@ -3004,8 +3223,9 @@
         <v>154</v>
       </c>
       <c r="G40" s="9"/>
-    </row>
-    <row r="41" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H40" s="13"/>
+    </row>
+    <row r="41" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>151</v>
       </c>
@@ -3025,8 +3245,9 @@
         <v>155</v>
       </c>
       <c r="G41" s="9"/>
-    </row>
-    <row r="42" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H41" s="13"/>
+    </row>
+    <row r="42" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>142</v>
       </c>
@@ -3046,8 +3267,9 @@
         <v>143</v>
       </c>
       <c r="G42" s="9"/>
-    </row>
-    <row r="43" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H42" s="13"/>
+    </row>
+    <row r="43" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>144</v>
       </c>
@@ -3067,8 +3289,9 @@
         <v>145</v>
       </c>
       <c r="G43" s="9"/>
-    </row>
-    <row r="44" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H43" s="13"/>
+    </row>
+    <row r="44" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>146</v>
       </c>
@@ -3088,8 +3311,9 @@
         <v>147</v>
       </c>
       <c r="G44" s="9"/>
-    </row>
-    <row r="45" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H44" s="13"/>
+    </row>
+    <row r="45" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>246</v>
       </c>
@@ -3109,8 +3333,9 @@
         <v>179</v>
       </c>
       <c r="G45" s="9"/>
-    </row>
-    <row r="46" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H45" s="13"/>
+    </row>
+    <row r="46" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>180</v>
       </c>
@@ -3130,8 +3355,9 @@
         <v>186</v>
       </c>
       <c r="G46" s="9"/>
-    </row>
-    <row r="47" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H46" s="13"/>
+    </row>
+    <row r="47" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>181</v>
       </c>
@@ -3151,8 +3377,9 @@
         <v>187</v>
       </c>
       <c r="G47" s="9"/>
-    </row>
-    <row r="48" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H47" s="13"/>
+    </row>
+    <row r="48" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>243</v>
       </c>
@@ -3172,8 +3399,9 @@
         <v>192</v>
       </c>
       <c r="G48" s="9"/>
-    </row>
-    <row r="49" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H48" s="13"/>
+    </row>
+    <row r="49" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>182</v>
       </c>
@@ -3193,8 +3421,11 @@
         <v>188</v>
       </c>
       <c r="G49" s="9"/>
-    </row>
-    <row r="50" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H49" s="13" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>183</v>
       </c>
@@ -3214,8 +3445,9 @@
         <v>189</v>
       </c>
       <c r="G50" s="9"/>
-    </row>
-    <row r="51" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H50" s="13"/>
+    </row>
+    <row r="51" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>184</v>
       </c>
@@ -3235,8 +3467,9 @@
         <v>190</v>
       </c>
       <c r="G51" s="9"/>
-    </row>
-    <row r="52" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H51" s="13"/>
+    </row>
+    <row r="52" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>185</v>
       </c>
@@ -3256,8 +3489,9 @@
         <v>191</v>
       </c>
       <c r="G52" s="9"/>
-    </row>
-    <row r="53" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H52" s="13"/>
+    </row>
+    <row r="53" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>193</v>
       </c>
@@ -3277,8 +3511,9 @@
         <v>194</v>
       </c>
       <c r="G53" s="9"/>
-    </row>
-    <row r="54" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H53" s="13"/>
+    </row>
+    <row r="54" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>196</v>
       </c>
@@ -3298,8 +3533,9 @@
         <v>197</v>
       </c>
       <c r="G54" s="9"/>
-    </row>
-    <row r="55" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H54" s="13"/>
+    </row>
+    <row r="55" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>198</v>
       </c>
@@ -3319,8 +3555,9 @@
         <v>199</v>
       </c>
       <c r="G55" s="9"/>
-    </row>
-    <row r="56" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H55" s="13"/>
+    </row>
+    <row r="56" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>200</v>
       </c>
@@ -3340,8 +3577,9 @@
         <v>201</v>
       </c>
       <c r="G56" s="9"/>
-    </row>
-    <row r="57" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H56" s="13"/>
+    </row>
+    <row r="57" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>202</v>
       </c>
@@ -3357,35 +3595,39 @@
       <c r="E57" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="F57" s="10" t="s">
+      <c r="F57" s="12" t="s">
         <v>203</v>
       </c>
       <c r="G57" s="9"/>
-    </row>
-    <row r="58" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
-        <v>204</v>
+      <c r="H57" s="13"/>
+    </row>
+    <row r="58" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="20" t="s">
+        <v>452</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>195</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="F58" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="G58" s="9"/>
-    </row>
-    <row r="59" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>449</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="F58" s="18" t="s">
+        <v>451</v>
+      </c>
+      <c r="G58" s="19">
+        <v>46246</v>
+      </c>
+      <c r="H58" s="13"/>
+    </row>
+    <row r="59" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>195</v>
@@ -3394,40 +3636,42 @@
         <v>75</v>
       </c>
       <c r="D59" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="G59" s="9"/>
+      <c r="H59" s="13"/>
+    </row>
+    <row r="60" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E60" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="F59" s="10" t="s">
+      <c r="F60" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="G59" s="9"/>
-    </row>
-    <row r="60" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
+      <c r="G60" s="9"/>
+      <c r="H60" s="13"/>
+    </row>
+    <row r="61" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="F60" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="G60" s="9"/>
-    </row>
-    <row r="61" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>208</v>
@@ -3436,19 +3680,20 @@
         <v>77</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G61" s="9"/>
-    </row>
-    <row r="62" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H61" s="13"/>
+    </row>
+    <row r="62" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>208</v>
@@ -3457,19 +3702,20 @@
         <v>77</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G62" s="9"/>
-    </row>
-    <row r="63" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H62" s="13"/>
+    </row>
+    <row r="63" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>208</v>
@@ -3481,142 +3727,151 @@
         <v>273</v>
       </c>
       <c r="E63" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="G63" s="9"/>
+      <c r="H63" s="13"/>
+    </row>
+    <row r="64" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E64" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="F63" s="10" t="s">
+      <c r="F64" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="G63" s="9"/>
-    </row>
-    <row r="64" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
+      <c r="G64" s="9"/>
+      <c r="H64" s="13"/>
+    </row>
+    <row r="65" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B65" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C65" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D65" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="E64" s="7" t="s">
+      <c r="E65" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="F64" s="10" t="s">
+      <c r="F65" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="G64" s="9"/>
-    </row>
-    <row r="65" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
+      <c r="G65" s="9"/>
+      <c r="H65" s="12" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="G65" s="9"/>
-    </row>
-    <row r="66" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>220</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>434</v>
+        <v>77</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>224</v>
+        <v>277</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>222</v>
       </c>
       <c r="G66" s="9"/>
-    </row>
-    <row r="67" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H66" s="13"/>
+    </row>
+    <row r="67" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>220</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>77</v>
+        <v>434</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="F67" s="10" t="s">
-        <v>226</v>
+        <v>278</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>224</v>
       </c>
       <c r="G67" s="9"/>
-    </row>
-    <row r="68" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H67" s="13"/>
+    </row>
+    <row r="68" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>220</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>434</v>
+        <v>77</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G68" s="9"/>
-    </row>
-    <row r="69" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H68" s="13"/>
+    </row>
+    <row r="69" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>220</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>77</v>
+        <v>434</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G69" s="9"/>
-    </row>
-    <row r="70" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H69" s="13"/>
+    </row>
+    <row r="70" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>220</v>
@@ -3625,84 +3880,88 @@
         <v>77</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G70" s="9"/>
-    </row>
-    <row r="71" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H70" s="13"/>
+    </row>
+    <row r="71" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>220</v>
       </c>
       <c r="C71" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="G71" s="9"/>
+      <c r="H71" s="13"/>
+    </row>
+    <row r="72" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C72" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="D72" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="E72" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="F71" s="10" t="s">
+      <c r="F72" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="G71" s="9"/>
-    </row>
-    <row r="72" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
+      <c r="G72" s="9"/>
+      <c r="H72" s="13"/>
+    </row>
+    <row r="73" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B73" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C73" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="D73" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="E72" s="7" t="s">
+      <c r="E73" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="F72" s="10" t="s">
+      <c r="F73" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="G72" s="9"/>
-    </row>
-    <row r="73" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
+      <c r="G73" s="9"/>
+      <c r="H73" s="13" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="6" t="s">
         <v>311</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="F73" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="G73" s="11">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
-        <v>312</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>120</v>
@@ -3714,18 +3973,19 @@
         <v>317</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G74" s="11">
         <v>46238</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H74" s="13"/>
+    </row>
+    <row r="75" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>120</v>
@@ -3737,202 +3997,211 @@
         <v>317</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G75" s="11">
         <v>46238</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H75" s="13"/>
+    </row>
+    <row r="76" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>76</v>
+        <v>346</v>
       </c>
       <c r="D76" s="7" t="s">
         <v>317</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G76" s="11">
         <v>46238</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H76" s="13"/>
+    </row>
+    <row r="77" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D77" s="7" t="s">
         <v>317</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G77" s="11">
         <v>46238</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H77" s="13"/>
+    </row>
+    <row r="78" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>434</v>
+        <v>75</v>
       </c>
       <c r="D78" s="7" t="s">
         <v>317</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G78" s="11">
         <v>46238</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H78" s="13"/>
+    </row>
+    <row r="79" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>77</v>
+        <v>434</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>330</v>
+        <v>355</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>323</v>
       </c>
       <c r="G79" s="11">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46238</v>
+      </c>
+      <c r="H79" s="13"/>
+    </row>
+    <row r="80" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>336</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F80" s="10" t="s">
-        <v>331</v>
+        <v>356</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>330</v>
       </c>
       <c r="G80" s="11">
         <v>46239</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H80" s="13"/>
+    </row>
+    <row r="81" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>336</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G81" s="11">
         <v>46239</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H81" s="13"/>
+    </row>
+    <row r="82" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>434</v>
+        <v>76</v>
       </c>
       <c r="D82" s="7" t="s">
         <v>336</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G82" s="11">
         <v>46239</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H82" s="13"/>
+    </row>
+    <row r="83" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>77</v>
+        <v>434</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>336</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G83" s="11">
         <v>46239</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H83" s="13"/>
+    </row>
+    <row r="84" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>120</v>
@@ -3944,39 +4213,43 @@
         <v>336</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G84" s="11">
         <v>46239</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H84" s="13"/>
+    </row>
+    <row r="85" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="G85" s="11">
+        <v>46239</v>
+      </c>
+      <c r="H85" s="13"/>
+    </row>
+    <row r="86" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="6" t="s">
         <v>337</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="F85" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="G85" s="9"/>
-    </row>
-    <row r="86" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="6" t="s">
-        <v>338</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>346</v>
@@ -3985,19 +4258,20 @@
         <v>346</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G86" s="9"/>
-    </row>
-    <row r="87" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H86" s="13"/>
+    </row>
+    <row r="87" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>346</v>
@@ -4006,42 +4280,42 @@
         <v>346</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G87" s="9"/>
-    </row>
-    <row r="88" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H87" s="13"/>
+    </row>
+    <row r="88" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>120</v>
+        <v>346</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>346</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>420</v>
+        <v>349</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>395</v>
+        <v>345</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="G88" s="11">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+      <c r="G88" s="9"/>
+      <c r="H88" s="13"/>
+    </row>
+    <row r="89" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>430</v>
+        <v>362</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>120</v>
@@ -4053,18 +4327,19 @@
         <v>420</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>431</v>
+        <v>385</v>
       </c>
       <c r="G89" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H89" s="13"/>
+    </row>
+    <row r="90" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>387</v>
+        <v>430</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>120</v>
@@ -4076,18 +4351,19 @@
         <v>420</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="G90" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H90" s="13"/>
+    </row>
+    <row r="91" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>120</v>
@@ -4099,18 +4375,19 @@
         <v>420</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G91" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H91" s="13"/>
+    </row>
+    <row r="92" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>120</v>
@@ -4122,18 +4399,19 @@
         <v>420</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G92" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H92" s="13"/>
+    </row>
+    <row r="93" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>120</v>
@@ -4145,18 +4423,19 @@
         <v>420</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G93" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H93" s="13"/>
+    </row>
+    <row r="94" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>120</v>
@@ -4168,18 +4447,19 @@
         <v>420</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G94" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H94" s="13"/>
+    </row>
+    <row r="95" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>120</v>
@@ -4191,41 +4471,43 @@
         <v>420</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G95" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H95" s="13"/>
+    </row>
+    <row r="96" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>76</v>
+        <v>346</v>
       </c>
       <c r="D96" s="7" t="s">
         <v>420</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G96" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H96" s="13"/>
+    </row>
+    <row r="97" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>120</v>
@@ -4237,18 +4519,19 @@
         <v>420</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G97" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H97" s="13"/>
+    </row>
+    <row r="98" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>120</v>
@@ -4260,41 +4543,43 @@
         <v>420</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="G98" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H98" s="13"/>
+    </row>
+    <row r="99" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>420</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G99" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H99" s="13"/>
+    </row>
+    <row r="100" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>120</v>
@@ -4306,64 +4591,67 @@
         <v>420</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G100" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H100" s="13"/>
+    </row>
+    <row r="101" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D101" s="7" t="s">
         <v>420</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G101" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H101" s="13"/>
+    </row>
+    <row r="102" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D102" s="7" t="s">
         <v>420</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G102" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H102" s="13"/>
+    </row>
+    <row r="103" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>120</v>
@@ -4375,18 +4663,19 @@
         <v>420</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G103" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H103" s="13"/>
+    </row>
+    <row r="104" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>120</v>
@@ -4398,18 +4687,19 @@
         <v>420</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G104" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H104" s="13"/>
+    </row>
+    <row r="105" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>120</v>
@@ -4421,41 +4711,43 @@
         <v>420</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G105" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H105" s="13"/>
+    </row>
+    <row r="106" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D106" s="7" t="s">
         <v>420</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G106" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H106" s="13"/>
+    </row>
+    <row r="107" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>120</v>
@@ -4467,18 +4759,19 @@
         <v>420</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="G107" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H107" s="13"/>
+    </row>
+    <row r="108" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>120</v>
@@ -4490,18 +4783,19 @@
         <v>420</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G108" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H108" s="13"/>
+    </row>
+    <row r="109" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>120</v>
@@ -4513,18 +4807,19 @@
         <v>420</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G109" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H109" s="13"/>
+    </row>
+    <row r="110" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>120</v>
@@ -4536,18 +4831,19 @@
         <v>420</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F110" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G110" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H110" s="13"/>
+    </row>
+    <row r="111" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>120</v>
@@ -4559,37 +4855,63 @@
         <v>420</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="F111" s="12" t="s">
-        <v>437</v>
+        <v>417</v>
+      </c>
+      <c r="F111" s="10" t="s">
+        <v>436</v>
       </c>
       <c r="G111" s="11">
         <v>46240</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H111" s="13"/>
+    </row>
+    <row r="112" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>434</v>
+        <v>77</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>420</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="F112" s="10" t="s">
-        <v>438</v>
+        <v>418</v>
+      </c>
+      <c r="F112" s="12" t="s">
+        <v>437</v>
       </c>
       <c r="G112" s="11">
         <v>46240</v>
       </c>
+      <c r="H112" s="13"/>
+    </row>
+    <row r="113" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="F113" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="G113" s="11">
+        <v>46240</v>
+      </c>
+      <c r="H113" s="15"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4602,15 +4924,21 @@
     <hyperlink ref="F13" r:id="rId7" xr:uid="{4281A67C-AC78-4A68-A664-CAB0381ADAA6}"/>
     <hyperlink ref="F17" r:id="rId8" xr:uid="{C020F178-7F0C-4255-84C0-D02096F78587}"/>
     <hyperlink ref="F19" r:id="rId9" xr:uid="{32919252-880A-47F2-A773-C93662E9BCDB}"/>
-    <hyperlink ref="F66" r:id="rId10" xr:uid="{D2B6880C-A11D-476C-9E19-250564686AE4}"/>
+    <hyperlink ref="F67" r:id="rId10" xr:uid="{D2B6880C-A11D-476C-9E19-250564686AE4}"/>
     <hyperlink ref="F46" r:id="rId11" xr:uid="{A8B4C01F-FFFA-442D-8753-183715E63934}"/>
-    <hyperlink ref="F79" r:id="rId12" xr:uid="{39785A4B-CDEC-4B2F-B0E5-38757511CF9A}"/>
-    <hyperlink ref="F111" r:id="rId13" xr:uid="{E2B870FB-FA48-41D9-B847-668BA958EB53}"/>
+    <hyperlink ref="F80" r:id="rId12" xr:uid="{39785A4B-CDEC-4B2F-B0E5-38757511CF9A}"/>
+    <hyperlink ref="F112" r:id="rId13" xr:uid="{E2B870FB-FA48-41D9-B847-668BA958EB53}"/>
+    <hyperlink ref="H25" r:id="rId14" xr:uid="{227644D8-9577-40DD-BC7F-062C17F6D549}"/>
+    <hyperlink ref="H65" r:id="rId15" xr:uid="{3689D33F-82C9-4FDD-B4F3-B446CDF73D1B}"/>
+    <hyperlink ref="H35" r:id="rId16" xr:uid="{268167CE-685E-4DE4-AB5E-4A9D1E7E89BA}"/>
+    <hyperlink ref="F36" r:id="rId17" xr:uid="{E7A90675-A8BF-4D56-8E6E-B5FB2D7576E4}"/>
+    <hyperlink ref="F57" r:id="rId18" xr:uid="{6CEA92B6-B814-47F7-BFE9-A75AB1E4F283}"/>
+    <hyperlink ref="F59" r:id="rId19" xr:uid="{16072CD9-EC50-4126-87EF-B53A54A6BE74}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId20"/>
   <tableParts count="1">
-    <tablePart r:id="rId15"/>
+    <tablePart r:id="rId21"/>
   </tableParts>
 </worksheet>
 </file>
